--- a/airline-dashboard/data/manual/airline_financial_data.xlsx
+++ b/airline-dashboard/data/manual/airline_financial_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trica\OneDrive\Documents\School\UNCC\Personal Projects\US Airlines Financials Project\airline_financials\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0f26b992e1a44723/Documents/GitHub Repos/airline_financials/airline-dashboard/data/manual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826EDDCB-8DC5-48D4-92ED-2287CEBE3206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{826EDDCB-8DC5-48D4-92ED-2287CEBE3206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{504DDDFE-45E9-48EE-AC9F-46D174CB1856}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CC2E0DD-0C2A-471D-BE08-E27D8B31800B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CC2E0DD-0C2A-471D-BE08-E27D8B31800B}"/>
   </bookViews>
   <sheets>
     <sheet name="airline_financials" sheetId="2" r:id="rId1"/>
@@ -957,22 +957,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95BF35CD-6CF2-4D2E-9294-3A1A732D8FBE}">
   <dimension ref="A1:K209"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="17.109375" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="17.140625" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2018</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>29000000</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2018</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>188000000</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2018</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>17000000</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2018</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>63000000</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2018</v>
       </c>
@@ -1176,7 +1176,7 @@
         <v>404000000</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2018</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>108000000</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2018</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>43000000</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2018</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>399000000</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2018</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>127000000</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2018</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2018</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>311000000</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2018</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>82000000</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2018</v>
       </c>
@@ -1450,7 +1450,7 @@
         <v>175000000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2018</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>1301000000</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2018</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>334000000</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2019</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2019</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>220000000</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2019</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>33000000</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2019</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>67000000</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2019</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>518000000</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2019</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>161000000</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2019</v>
       </c>
@@ -1759,7 +1759,7 @@
         <v>52000000</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2019</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>517000000</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2019</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>174000000</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2019</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>74000000</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2019</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>387000000</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2019</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>123000000</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2019</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>213000000</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2019</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>1643000000</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2019</v>
       </c>
@@ -2036,7 +2036,7 @@
         <v>491000000</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2020</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2020</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2020</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2020</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2020</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2020</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2020</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2020</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2020</v>
       </c>
@@ -2342,7 +2342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2020</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2020</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2020</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2020</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2020</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2020</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2021</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2021</v>
       </c>
@@ -2622,7 +2622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2021</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2021</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2021</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2021</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2021</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2021</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2021</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2021</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2021</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2021</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2021</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2021</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2021</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2022</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2022</v>
       </c>
@@ -3138,7 +3138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2022</v>
       </c>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>2022</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>64000000</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>2022</v>
       </c>
@@ -3240,7 +3240,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>2022</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>2022</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>59000000</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>2022</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>237000000</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>2022</v>
       </c>
@@ -3374,7 +3374,7 @@
         <v>8000000</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>2022</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>88000000</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>2022</v>
       </c>
@@ -3444,7 +3444,7 @@
         <v>272000000</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>2022</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>125000000</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>2022</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>211000000</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>2022</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>563000000</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>2022</v>
       </c>
@@ -3584,7 +3584,7 @@
         <v>133000000</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>2023</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>2023</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>72000000</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>2023</v>
       </c>
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>2023</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>173000000</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>2023</v>
       </c>
@@ -3756,7 +3756,7 @@
         <v>595000000</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>2023</v>
       </c>
@@ -3788,7 +3788,7 @@
         <v>220000000</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>2023</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>2023</v>
       </c>
@@ -3858,7 +3858,7 @@
         <v>417000000</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>2023</v>
       </c>
@@ -3890,7 +3890,7 @@
         <v>301000000</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>2023</v>
       </c>
@@ -3925,7 +3925,7 @@
         <v>53000000</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>2023</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>299000000</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>2023</v>
       </c>
@@ -3995,7 +3995,7 @@
         <v>160000000</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>2023</v>
       </c>
@@ -4030,7 +4030,7 @@
         <v>261000000</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>2023</v>
       </c>
@@ -4065,7 +4065,7 @@
         <v>1383000000</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>2023</v>
       </c>
@@ -4100,7 +4100,7 @@
         <v>681000000</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>2024</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>610559</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>2024</v>
       </c>
@@ -4171,7 +4171,7 @@
         <v>125000000</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>2024</v>
       </c>
@@ -4203,7 +4203,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>2024</v>
       </c>
@@ -4239,7 +4239,7 @@
         <v>120716144</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>2024</v>
       </c>
@@ -4274,7 +4274,7 @@
         <v>519000000</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>2024</v>
       </c>
@@ -4306,7 +4306,7 @@
         <v>185000000</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>2024</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>7762816</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2024</v>
       </c>
@@ -4377,7 +4377,7 @@
         <v>320000000</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>2024</v>
       </c>
@@ -4409,7 +4409,7 @@
         <v>231000000</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>2017</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>241000000</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>2016</v>
       </c>
@@ -4479,7 +4479,7 @@
         <v>314000000</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>2015</v>
       </c>
@@ -4514,7 +4514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>2014</v>
       </c>
@@ -4549,7 +4549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>2017</v>
       </c>
@@ -4584,7 +4584,7 @@
         <v>1065000000</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>2016</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>1115000000</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2015</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>1490000000</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>2014</v>
       </c>
@@ -4689,7 +4689,7 @@
         <v>1085000000</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>2017</v>
       </c>
@@ -4724,7 +4724,7 @@
         <v>349000000</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>2016</v>
       </c>
@@ -4759,7 +4759,7 @@
         <v>628000000</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>2015</v>
       </c>
@@ -4794,7 +4794,7 @@
         <v>698000000</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>2014</v>
       </c>
@@ -4829,7 +4829,7 @@
         <v>235000000</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>2023</v>
       </c>
@@ -4864,7 +4864,7 @@
         <v>110000000</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>2022</v>
       </c>
@@ -4899,7 +4899,7 @@
         <v>127000000</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>2021</v>
       </c>
@@ -4934,7 +4934,7 @@
         <v>230000000</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>2020</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>2019</v>
       </c>
@@ -5004,7 +5004,7 @@
         <v>695000000</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>2018</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>580000000</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>2017</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>579000000</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>2016</v>
       </c>
@@ -5109,7 +5109,7 @@
         <v>645000000</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>2015</v>
       </c>
@@ -5144,7 +5144,7 @@
         <v>655000000</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>2014</v>
       </c>
@@ -5179,7 +5179,7 @@
         <v>374000000</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2024</v>
       </c>
@@ -5214,7 +5214,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2024</v>
       </c>
@@ -5249,7 +5249,7 @@
         <v>31000000</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2024</v>
       </c>
@@ -5284,7 +5284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2017</v>
       </c>
@@ -5319,7 +5319,7 @@
         <v>31000000</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2017</v>
       </c>
@@ -5354,7 +5354,7 @@
         <v>94000000</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>2017</v>
       </c>
@@ -5389,7 +5389,7 @@
         <v>70000000</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>2017</v>
       </c>
@@ -5424,7 +5424,7 @@
         <v>47000000</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>2016</v>
       </c>
@@ -5459,7 +5459,7 @@
         <v>73000000</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>2016</v>
       </c>
@@ -5494,7 +5494,7 @@
         <v>98000000</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>2016</v>
       </c>
@@ -5529,7 +5529,7 @@
         <v>86000000</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2016</v>
       </c>
@@ -5564,7 +5564,7 @@
         <v>57000000</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2015</v>
       </c>
@@ -5599,7 +5599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2015</v>
       </c>
@@ -5634,7 +5634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2015</v>
       </c>
@@ -5669,7 +5669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>2015</v>
       </c>
@@ -5704,7 +5704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2014</v>
       </c>
@@ -5739,7 +5739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2014</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>2014</v>
       </c>
@@ -5809,7 +5809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2014</v>
       </c>
@@ -5844,7 +5844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2017</v>
       </c>
@@ -5876,7 +5876,7 @@
         <v>151000000</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2017</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>338000000</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2017</v>
       </c>
@@ -5940,7 +5940,7 @@
         <v>314000000</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2017</v>
       </c>
@@ -5975,7 +5975,7 @@
         <v>262000000</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>2016</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>272000000</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2016</v>
       </c>
@@ -6039,7 +6039,7 @@
         <v>324000000</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2016</v>
       </c>
@@ -6071,7 +6071,7 @@
         <v>326000000</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2016</v>
       </c>
@@ -6106,7 +6106,7 @@
         <v>193000000</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2015</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>136000000</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2015</v>
       </c>
@@ -6170,7 +6170,7 @@
         <v>411000000</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2015</v>
       </c>
@@ -6202,7 +6202,7 @@
         <v>563000000</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2015</v>
       </c>
@@ -6237,7 +6237,7 @@
         <v>380000000</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2014</v>
       </c>
@@ -6269,7 +6269,7 @@
         <v>99000000</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2014</v>
       </c>
@@ -6301,7 +6301,7 @@
         <v>340000000</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2014</v>
       </c>
@@ -6333,7 +6333,7 @@
         <v>384000000</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2014</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>262000000</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2017</v>
       </c>
@@ -6400,7 +6400,7 @@
         <v>28000000</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2017</v>
       </c>
@@ -6432,7 +6432,7 @@
         <v>140000000</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2017</v>
       </c>
@@ -6464,7 +6464,7 @@
         <v>109000000</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2017</v>
       </c>
@@ -6499,7 +6499,7 @@
         <v>73000000</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2016</v>
       </c>
@@ -6531,7 +6531,7 @@
         <v>94000000</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2016</v>
       </c>
@@ -6563,7 +6563,7 @@
         <v>153000000</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2016</v>
       </c>
@@ -6595,7 +6595,7 @@
         <v>235000000</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2016</v>
       </c>
@@ -6630,7 +6630,7 @@
         <v>145000000</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>2015</v>
       </c>
@@ -6662,7 +6662,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2015</v>
       </c>
@@ -6694,7 +6694,7 @@
         <v>195000000</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2015</v>
       </c>
@@ -6726,7 +6726,7 @@
         <v>257000000</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2015</v>
       </c>
@@ -6761,7 +6761,7 @@
         <v>146000000</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2014</v>
       </c>
@@ -6793,7 +6793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2014</v>
       </c>
@@ -6825,7 +6825,7 @@
         <v>78000000</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2014</v>
       </c>
@@ -6857,7 +6857,7 @@
         <v>103000000</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>2014</v>
       </c>
@@ -6892,7 +6892,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>2024</v>
       </c>
@@ -6927,7 +6927,7 @@
         <v>425000000</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>2024</v>
       </c>
@@ -6962,7 +6962,7 @@
         <v>1389000000</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>2024</v>
       </c>
@@ -6997,7 +6997,7 @@
         <v>294000000</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>2024</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>713000000</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2024</v>
       </c>
@@ -7068,7 +7068,7 @@
         <v>98910482</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2024</v>
       </c>
@@ -7103,7 +7103,7 @@
         <v>228000000</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2024</v>
       </c>
@@ -7138,7 +7138,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>2024</v>
       </c>
@@ -7173,7 +7173,7 @@
         <v>103000000</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>2025</v>
       </c>
@@ -7208,7 +7208,7 @@
         <v>124000000</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>2025</v>
       </c>
@@ -7240,7 +7240,7 @@
         <v>43000000</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>2025</v>
       </c>
@@ -7275,7 +7275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>2025</v>
       </c>
@@ -7310,7 +7310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>2025</v>
       </c>
@@ -7345,7 +7345,7 @@
         <v>470000000</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>2025</v>
       </c>
@@ -7377,7 +7377,7 @@
         <v>188000000</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>2025</v>
       </c>
@@ -7409,11 +7409,10 @@
         <v>24217000000</v>
       </c>
       <c r="K188">
-        <f>ROUND($K$201*(((D188-F188)/($D$201-$F$201))/(((D200-F200)/($D$201-$F$201))+((D188-F188)/($D$201-$F$201)))),0)</f>
-        <v>39360025</v>
-      </c>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+        <v>41000000</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>2025</v>
       </c>
@@ -7448,7 +7447,7 @@
         <v>14000000</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>2025</v>
       </c>
@@ -7483,7 +7482,7 @@
         <v>392000000</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>2025</v>
       </c>
@@ -7515,7 +7514,7 @@
         <v>228000000</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>2025</v>
       </c>
@@ -7550,7 +7549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>2025</v>
       </c>
@@ -7585,7 +7584,7 @@
         <v>11000000</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>2025</v>
       </c>
@@ -7620,7 +7619,7 @@
         <v>351000000</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>2025</v>
       </c>
@@ -7655,7 +7654,7 @@
         <v>1337000000</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>2025</v>
       </c>
@@ -7690,7 +7689,7 @@
         <v>244000000</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>2025</v>
       </c>
@@ -7725,7 +7724,7 @@
         <v>704000000</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>2025</v>
       </c>
@@ -7760,7 +7759,7 @@
         <v>71000000</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>2025</v>
       </c>
@@ -7795,7 +7794,7 @@
         <v>97000000</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>2025</v>
       </c>
@@ -7831,7 +7830,7 @@
         <v>15639975</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>2025</v>
       </c>
@@ -7866,7 +7865,7 @@
         <v>55000000</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>2026</v>
       </c>
@@ -7901,7 +7900,7 @@
         <v>165000000</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>2026</v>
       </c>
@@ -7933,7 +7932,7 @@
         <v>59000000</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>2026</v>
       </c>
@@ -7968,7 +7967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>2026</v>
       </c>
@@ -8003,7 +8002,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>2026</v>
       </c>
@@ -8038,7 +8037,7 @@
         <v>328000000</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>2026</v>
       </c>
@@ -8070,7 +8069,7 @@
         <v>90000000</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>2026</v>
       </c>
@@ -8080,8 +8079,29 @@
       <c r="C208" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D208">
+        <v>16735000000</v>
+      </c>
+      <c r="E208">
+        <v>15214000000</v>
+      </c>
+      <c r="F208">
+        <v>16289000000</v>
+      </c>
+      <c r="G208">
+        <v>71000000</v>
+      </c>
+      <c r="H208">
+        <v>68118000000</v>
+      </c>
+      <c r="I208">
+        <v>81843000000</v>
+      </c>
+      <c r="K208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>2026</v>
       </c>
@@ -8090,6 +8110,27 @@
       </c>
       <c r="C209" t="s">
         <v>13</v>
+      </c>
+      <c r="D209">
+        <v>8432000000</v>
+      </c>
+      <c r="E209">
+        <v>7745000000</v>
+      </c>
+      <c r="F209">
+        <v>8147000000</v>
+      </c>
+      <c r="G209">
+        <v>285000000</v>
+      </c>
+      <c r="H209">
+        <v>37346000000</v>
+      </c>
+      <c r="I209">
+        <v>47093000000</v>
+      </c>
+      <c r="K209">
+        <v>53000000</v>
       </c>
     </row>
   </sheetData>
@@ -8100,13 +8141,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47E8CB36-28FD-4A01-8E6F-FAD97027E6F9}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8123,7 +8164,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2013</v>
       </c>
@@ -8140,7 +8181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2014</v>
       </c>
@@ -8157,7 +8198,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2015</v>
       </c>
@@ -8174,7 +8215,7 @@
         <v>3600000000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2016</v>
       </c>
@@ -8191,7 +8232,7 @@
         <v>4400000000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2017</v>
       </c>
@@ -8208,7 +8249,7 @@
         <v>1600000000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2018</v>
       </c>
@@ -8225,7 +8266,7 @@
         <v>800000000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2019</v>
       </c>
@@ -8242,7 +8283,7 @@
         <v>1100000000</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2020</v>
       </c>
@@ -8259,7 +8300,7 @@
         <v>145000000</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2013</v>
       </c>
@@ -8276,7 +8317,7 @@
         <v>250000000</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2014</v>
       </c>
@@ -8293,7 +8334,7 @@
         <v>1100000000</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2015</v>
       </c>
@@ -8310,7 +8351,7 @@
         <v>2200000000</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2016</v>
       </c>
@@ -8327,7 +8368,7 @@
         <v>2600000000</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2017</v>
       </c>
@@ -8344,7 +8385,7 @@
         <v>1700000000</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2018</v>
       </c>
@@ -8361,7 +8402,7 @@
         <v>1600000000</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2019</v>
       </c>
@@ -8378,7 +8419,7 @@
         <v>2000000000</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2020</v>
       </c>
@@ -8395,7 +8436,7 @@
         <v>377620000</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2013</v>
       </c>
@@ -8412,7 +8453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2014</v>
       </c>
@@ -8429,7 +8470,7 @@
         <v>320000000</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2015</v>
       </c>
@@ -8446,7 +8487,7 @@
         <v>1200000000</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2016</v>
       </c>
@@ -8463,7 +8504,7 @@
         <v>2600000000</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2017</v>
       </c>
@@ -8480,7 +8521,7 @@
         <v>1800000000</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2018</v>
       </c>
@@ -8497,7 +8538,7 @@
         <v>1200000000</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2019</v>
       </c>
@@ -8514,7 +8555,7 @@
         <v>1600000000</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2020</v>
       </c>
@@ -8539,16 +8580,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{490D347E-B079-4188-B046-54C6AF8BB324}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8565,7 +8606,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2020</v>
       </c>
@@ -8582,7 +8623,7 @@
         <v>1901355562.5899999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2021</v>
       </c>
@@ -8599,7 +8640,7 @@
         <v>1082205377.28</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2020</v>
       </c>
@@ -8616,7 +8657,7 @@
         <v>158535000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2021</v>
       </c>
@@ -8633,7 +8674,7 @@
         <v>83433000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2020</v>
       </c>
@@ -8650,7 +8691,7 @@
         <v>2293578491.5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2021</v>
       </c>

--- a/airline-dashboard/data/manual/airline_financial_data.xlsx
+++ b/airline-dashboard/data/manual/airline_financial_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0f26b992e1a44723/Documents/GitHub Repos/airline_financials/airline-dashboard/data/manual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{826EDDCB-8DC5-48D4-92ED-2287CEBE3206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{504DDDFE-45E9-48EE-AC9F-46D174CB1856}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{826EDDCB-8DC5-48D4-92ED-2287CEBE3206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{623539DB-94CE-4819-82FE-06D2F853BFFB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CC2E0DD-0C2A-471D-BE08-E27D8B31800B}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="20">
   <si>
     <t>Year</t>
   </si>
@@ -639,6 +639,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -956,7 +960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95BF35CD-6CF2-4D2E-9294-3A1A732D8FBE}">
-  <dimension ref="A1:K209"/>
+  <dimension ref="A1:K249"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
@@ -4132,7 +4136,7 @@
         <v>27853000000</v>
       </c>
       <c r="K92">
-        <f>ROUND($K$179*((D92-F92)/($D$179-$F$179)),0)</f>
+        <f>ROUND($K$219*((D92-F92)/($D$219-$F$219)),0)</f>
         <v>610559</v>
       </c>
     </row>
@@ -4235,7 +4239,7 @@
         <v>27209000000</v>
       </c>
       <c r="K95">
-        <f>ROUND($K$179*((D95-F95)/($D$179-$F$179)),0)</f>
+        <f>ROUND($K$219*((D95-F95)/($D$219-$F$219)),0)</f>
         <v>120716144</v>
       </c>
     </row>
@@ -4338,7 +4342,7 @@
         <v>25848000000</v>
       </c>
       <c r="K98">
-        <f>ROUND($K$179*((D98-F98)/($D$179-$F$179)),0)</f>
+        <f>ROUND($K$219*((D98-F98)/($D$219-$F$219)),0)</f>
         <v>7762816</v>
       </c>
     </row>
@@ -4861,7 +4865,7 @@
         <v>7978000000</v>
       </c>
       <c r="K113">
-        <v>110000000</v>
+        <v>118000000</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -5001,7 +5005,7 @@
         <v>1846000000</v>
       </c>
       <c r="K117">
-        <v>695000000</v>
+        <v>667000000</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -5036,7 +5040,7 @@
         <v>2771000000</v>
       </c>
       <c r="K118">
-        <v>580000000</v>
+        <v>544000000</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -5071,7 +5075,7 @@
         <v>3320000000</v>
       </c>
       <c r="K119">
-        <v>579000000</v>
+        <v>543000000</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -5106,7 +5110,7 @@
         <v>2821000000</v>
       </c>
       <c r="K120">
-        <v>645000000</v>
+        <v>586000000</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -5141,7 +5145,7 @@
         <v>2541000000</v>
       </c>
       <c r="K121">
-        <v>655000000</v>
+        <v>620000000</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -5176,47 +5180,35 @@
         <v>2434000000</v>
       </c>
       <c r="K122">
-        <v>374000000</v>
+        <v>355000000</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="B123">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C123" t="s">
         <v>13</v>
       </c>
-      <c r="D123">
-        <v>6870000000</v>
-      </c>
       <c r="E123">
-        <v>6250000000</v>
-      </c>
-      <c r="F123">
-        <v>6832000000</v>
-      </c>
-      <c r="G123">
-        <v>67000000</v>
+        <v>3933000000</v>
       </c>
       <c r="H123">
-        <v>36735000000</v>
+        <v>24155317000</v>
       </c>
       <c r="I123">
-        <v>45219000000</v>
-      </c>
-      <c r="J123">
-        <v>5075000000</v>
+        <v>30474582000</v>
       </c>
       <c r="K123">
-        <v>18000000</v>
+        <v>29000000</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="B124">
         <v>2</v>
@@ -5224,239 +5216,155 @@
       <c r="C124" t="s">
         <v>13</v>
       </c>
-      <c r="D124">
-        <v>7354000000</v>
-      </c>
       <c r="E124">
-        <v>6712000000</v>
-      </c>
-      <c r="F124">
-        <v>6956000000</v>
-      </c>
-      <c r="G124">
-        <v>367000000</v>
+        <v>4752000000</v>
       </c>
       <c r="H124">
-        <v>38221000000</v>
+        <v>28589997000</v>
       </c>
       <c r="I124">
-        <v>46250000000</v>
-      </c>
-      <c r="J124">
-        <v>5065000000</v>
+        <v>34096212000</v>
       </c>
       <c r="K124">
-        <v>31000000</v>
+        <v>127000000</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C125" t="s">
         <v>13</v>
       </c>
-      <c r="D125">
-        <v>6329000000</v>
-      </c>
       <c r="E125">
-        <v>5712000000</v>
-      </c>
-      <c r="F125">
-        <v>6722000000</v>
-      </c>
-      <c r="G125">
-        <v>-231000000</v>
+        <v>4564000000</v>
       </c>
       <c r="H125">
-        <v>33087000000</v>
+        <v>28522164000</v>
       </c>
       <c r="I125">
-        <v>42248000000</v>
-      </c>
-      <c r="J125">
-        <v>7974000000</v>
+        <v>33785824000</v>
       </c>
       <c r="K125">
-        <v>0</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C126" t="s">
-        <v>5</v>
-      </c>
-      <c r="D126">
-        <v>9624000000</v>
+        <v>13</v>
       </c>
       <c r="E126">
-        <v>8155000000</v>
-      </c>
-      <c r="F126">
-        <v>9023000000</v>
-      </c>
-      <c r="G126">
-        <v>234000000</v>
+        <v>4409000000</v>
       </c>
       <c r="H126">
-        <v>50984000000</v>
+        <v>26767655000</v>
       </c>
       <c r="I126">
-        <v>64341000000</v>
-      </c>
-      <c r="J126">
-        <v>22829000000</v>
+        <v>32647338000</v>
       </c>
       <c r="K126">
-        <v>31000000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C127" t="s">
-        <v>5</v>
-      </c>
-      <c r="D127">
-        <v>11105000000</v>
+        <v>13</v>
       </c>
       <c r="E127">
-        <v>9582000000</v>
-      </c>
-      <c r="F127">
-        <v>9570000000</v>
-      </c>
-      <c r="G127">
-        <v>803000000</v>
+        <v>4178000000</v>
       </c>
       <c r="H127">
-        <v>59564000000</v>
+        <v>25860866000</v>
       </c>
       <c r="I127">
-        <v>71743000000</v>
-      </c>
-      <c r="J127">
-        <v>22525000000</v>
+        <v>32297465000</v>
       </c>
       <c r="K127">
-        <v>94000000</v>
+        <v>126000000</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B128">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C128" t="s">
-        <v>5</v>
-      </c>
-      <c r="D128">
-        <v>10878000000</v>
+        <v>13</v>
       </c>
       <c r="E128">
-        <v>9377000000</v>
-      </c>
-      <c r="F128">
-        <v>9646000000</v>
-      </c>
-      <c r="G128">
-        <v>624000000</v>
+        <v>4852000000</v>
       </c>
       <c r="H128">
-        <v>54012000000</v>
+        <v>30858381000</v>
       </c>
       <c r="I128">
-        <v>64582000000</v>
-      </c>
-      <c r="J128">
-        <v>22217000000</v>
+        <v>36476030000</v>
       </c>
       <c r="K128">
-        <v>70000000</v>
+        <v>182000000</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B129">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C129" t="s">
-        <v>5</v>
-      </c>
-      <c r="D129">
-        <v>10600000000</v>
+        <v>13</v>
       </c>
       <c r="E129">
-        <v>9019000000</v>
-      </c>
-      <c r="F129">
-        <v>9910000000</v>
-      </c>
-      <c r="G129">
-        <v>258000000</v>
+        <v>4716000000</v>
       </c>
       <c r="H129">
-        <v>55327000000</v>
+        <v>31052660000</v>
       </c>
       <c r="I129">
-        <v>67355000000</v>
-      </c>
-      <c r="J129">
-        <v>22511000000</v>
+        <v>36360340000</v>
       </c>
       <c r="K129">
-        <v>47000000</v>
+        <v>177000000</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B130">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C130" t="s">
-        <v>5</v>
-      </c>
-      <c r="D130">
-        <v>9435000000</v>
+        <v>13</v>
       </c>
       <c r="E130">
-        <v>8087000000</v>
-      </c>
-      <c r="F130">
-        <v>8100000000</v>
-      </c>
-      <c r="G130">
-        <v>700000000</v>
+        <v>4553000000</v>
       </c>
       <c r="H130">
-        <v>51771000000</v>
+        <v>29727972000</v>
       </c>
       <c r="I130">
-        <v>65064000000</v>
-      </c>
-      <c r="J130">
-        <v>19134000000</v>
+        <v>35367574000</v>
       </c>
       <c r="K130">
-        <v>73000000</v>
+        <v>136000000</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -5464,34 +5372,22 @@
         <v>2016</v>
       </c>
       <c r="B131">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C131" t="s">
-        <v>5</v>
-      </c>
-      <c r="D131">
-        <v>10363000000</v>
+        <v>13</v>
       </c>
       <c r="E131">
-        <v>8995000000</v>
-      </c>
-      <c r="F131">
-        <v>8612000000</v>
-      </c>
-      <c r="G131">
-        <v>950000000</v>
+        <v>4398000000</v>
       </c>
       <c r="H131">
-        <v>58336000000</v>
+        <v>28408164000</v>
       </c>
       <c r="I131">
-        <v>70751000000</v>
-      </c>
-      <c r="J131">
-        <v>21131000000</v>
+        <v>35268149000</v>
       </c>
       <c r="K131">
-        <v>98000000</v>
+        <v>155000000</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
@@ -5499,34 +5395,22 @@
         <v>2016</v>
       </c>
       <c r="B132">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C132" t="s">
-        <v>5</v>
-      </c>
-      <c r="D132">
-        <v>10594000000</v>
+        <v>13</v>
       </c>
       <c r="E132">
-        <v>9150000000</v>
-      </c>
-      <c r="F132">
-        <v>9163000000</v>
-      </c>
-      <c r="G132">
-        <v>737000000</v>
+        <v>4905000000</v>
       </c>
       <c r="H132">
-        <v>53472000000</v>
+        <v>32707694000</v>
       </c>
       <c r="I132">
-        <v>63751000000</v>
-      </c>
-      <c r="J132">
-        <v>21545000000</v>
+        <v>38225282000</v>
       </c>
       <c r="K132">
-        <v>86000000</v>
+        <v>206000000</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
@@ -5534,1648 +5418,1359 @@
         <v>2016</v>
       </c>
       <c r="B133">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C133" t="s">
-        <v>5</v>
-      </c>
-      <c r="D133">
-        <v>9789000000</v>
+        <v>13</v>
       </c>
       <c r="E133">
-        <v>8347000000</v>
-      </c>
-      <c r="F133">
-        <v>9022000000</v>
-      </c>
-      <c r="G133">
-        <v>289000000</v>
+        <v>4669000000</v>
       </c>
       <c r="H133">
-        <v>53452000000</v>
+        <v>32315952000</v>
       </c>
       <c r="I133">
-        <v>65683000000</v>
-      </c>
-      <c r="J133">
-        <v>22489000000</v>
+        <v>37881510000</v>
       </c>
       <c r="K133">
-        <v>57000000</v>
+        <v>101000000</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C134" t="s">
-        <v>5</v>
-      </c>
-      <c r="D134">
-        <v>9827000000</v>
+        <v>13</v>
       </c>
       <c r="E134">
-        <v>8441000000</v>
-      </c>
-      <c r="F134">
-        <v>8611000000</v>
-      </c>
-      <c r="G134">
-        <v>932000000</v>
+        <v>4623000000</v>
       </c>
       <c r="H134">
-        <v>50190000000</v>
+        <v>31366176000</v>
       </c>
       <c r="I134">
-        <v>62791000000</v>
-      </c>
-      <c r="J134">
-        <v>17638000000</v>
+        <v>37147109000</v>
       </c>
       <c r="K134">
-        <v>0</v>
+        <v>123000000</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C135" t="s">
-        <v>5</v>
-      </c>
-      <c r="D135">
-        <v>10827000000</v>
+        <v>13</v>
       </c>
       <c r="E135">
-        <v>9414000000</v>
-      </c>
-      <c r="F135">
-        <v>8906000000</v>
-      </c>
-      <c r="G135">
-        <v>1704000000</v>
+        <v>4424000000</v>
       </c>
       <c r="H135">
-        <v>57821000000</v>
+        <v>29340658000</v>
       </c>
       <c r="I135">
-        <v>69401000000</v>
-      </c>
-      <c r="J135">
-        <v>17152000000</v>
+        <v>36699870000</v>
       </c>
       <c r="K135">
-        <v>0</v>
+        <v>99000000</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B136">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C136" t="s">
-        <v>5</v>
-      </c>
-      <c r="D136">
-        <v>10706000000</v>
+        <v>13</v>
       </c>
       <c r="E136">
-        <v>9353000000</v>
-      </c>
-      <c r="F136">
-        <v>8707000000</v>
-      </c>
-      <c r="G136">
-        <v>1693000000</v>
+        <v>5233000000</v>
       </c>
       <c r="H136">
-        <v>60866000000</v>
+        <v>34382696000</v>
       </c>
       <c r="I136">
-        <v>71092000000</v>
-      </c>
-      <c r="J136">
-        <v>18849000000</v>
+        <v>40171225000</v>
       </c>
       <c r="K136">
-        <v>0</v>
+        <v>202000000</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B137">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C137" t="s">
-        <v>5</v>
-      </c>
-      <c r="D137">
-        <v>9630000000</v>
+        <v>13</v>
       </c>
       <c r="E137">
-        <v>8305000000</v>
-      </c>
-      <c r="F137">
-        <v>8562000000</v>
-      </c>
-      <c r="G137">
-        <v>3281000000</v>
+        <v>4745000000</v>
       </c>
       <c r="H137">
-        <v>54133000000</v>
+        <v>33128227000</v>
       </c>
       <c r="I137">
-        <v>65453000000</v>
-      </c>
-      <c r="J137">
-        <v>18330000000</v>
+        <v>39053164000</v>
       </c>
       <c r="K137">
-        <v>0</v>
+        <v>127000000</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C138" t="s">
-        <v>5</v>
-      </c>
-      <c r="D138">
-        <v>9995000000</v>
+        <v>13</v>
       </c>
       <c r="E138">
-        <v>8665000000</v>
-      </c>
-      <c r="F138">
-        <v>9265000000</v>
-      </c>
-      <c r="G138">
-        <v>480000000</v>
+        <v>4738000000</v>
       </c>
       <c r="H138">
-        <v>50886000000</v>
+        <v>32189839000</v>
       </c>
       <c r="I138">
-        <v>63392000000</v>
-      </c>
-      <c r="J138">
-        <v>15244000000</v>
+        <v>37886814000</v>
       </c>
       <c r="K138">
-        <v>0</v>
+        <v>115000000</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="B139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C139" t="s">
-        <v>5</v>
-      </c>
-      <c r="D139">
-        <v>11355000000</v>
+        <v>13</v>
       </c>
       <c r="E139">
-        <v>9920000000</v>
-      </c>
-      <c r="F139">
-        <v>9956000000</v>
-      </c>
-      <c r="G139">
-        <v>864000000</v>
+        <v>4585000000</v>
       </c>
       <c r="H139">
-        <v>57194000000</v>
+        <v>30439000000</v>
       </c>
       <c r="I139">
-        <v>68090000000</v>
-      </c>
-      <c r="J139">
-        <v>15205000000</v>
+        <v>37366000000</v>
       </c>
       <c r="K139">
-        <v>0</v>
+        <v>102000000</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="B140">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C140" t="s">
-        <v>5</v>
-      </c>
-      <c r="D140">
-        <v>11139000000</v>
+        <v>13</v>
       </c>
       <c r="E140">
-        <v>9758000000</v>
-      </c>
-      <c r="F140">
-        <v>9879000000</v>
-      </c>
-      <c r="G140">
-        <v>942000000</v>
+        <v>5358000000</v>
       </c>
       <c r="H140">
-        <v>57650000000</v>
+        <v>35143000000</v>
       </c>
       <c r="I140">
-        <v>69120000000</v>
-      </c>
-      <c r="J140">
-        <v>15651000000</v>
+        <v>41492000000</v>
       </c>
       <c r="K140">
-        <v>0</v>
+        <v>166000000</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="B141">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C141" t="s">
-        <v>5</v>
-      </c>
-      <c r="D141">
-        <v>10160000000</v>
+        <v>13</v>
       </c>
       <c r="E141">
-        <v>8782000000</v>
-      </c>
-      <c r="F141">
-        <v>9300000000</v>
-      </c>
-      <c r="G141">
-        <v>597000000</v>
+        <v>5194000000</v>
       </c>
       <c r="H141">
-        <v>52140000000</v>
+        <v>34024000000</v>
       </c>
       <c r="I141">
-        <v>65053000000</v>
-      </c>
-      <c r="J141">
-        <v>16196000000</v>
+        <v>40570000000</v>
       </c>
       <c r="K141">
-        <v>0</v>
+        <v>135000000</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C142" t="s">
-        <v>6</v>
-      </c>
-      <c r="D142">
-        <v>9148000000</v>
+        <v>13</v>
       </c>
       <c r="E142">
-        <v>7688000000</v>
-      </c>
-      <c r="F142">
-        <v>8095000000</v>
-      </c>
-      <c r="G142">
-        <v>603000000</v>
+        <v>5317000000</v>
       </c>
       <c r="H142">
-        <v>47952000000</v>
+        <v>33716000000</v>
       </c>
       <c r="I142">
-        <v>57871000000</v>
+        <v>40367000000</v>
       </c>
       <c r="K142">
-        <v>151000000</v>
+        <v>141000000</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="B143">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C143" t="s">
-        <v>6</v>
-      </c>
-      <c r="D143">
-        <v>10791000000</v>
+        <v>13</v>
       </c>
       <c r="E143">
-        <v>9231000000</v>
-      </c>
-      <c r="F143">
-        <v>8763000000</v>
-      </c>
-      <c r="G143">
-        <v>1224000000</v>
+        <v>4745000000</v>
       </c>
       <c r="H143">
-        <v>57575000000</v>
+        <v>30704000000</v>
       </c>
       <c r="I143">
-        <v>66227000000</v>
+        <v>37885000000</v>
       </c>
       <c r="K143">
-        <v>338000000</v>
+        <v>88000000</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="B144">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C144" t="s">
-        <v>6</v>
-      </c>
-      <c r="D144">
-        <v>11060000000</v>
+        <v>13</v>
       </c>
       <c r="E144">
-        <v>9399000000</v>
-      </c>
-      <c r="F144">
-        <v>9221000000</v>
-      </c>
-      <c r="G144">
-        <v>1178000000</v>
+        <v>5487000000</v>
       </c>
       <c r="H144">
-        <v>61006000000</v>
+        <v>34528000000</v>
       </c>
       <c r="I144">
-        <v>70167000000</v>
+        <v>39985000000</v>
       </c>
       <c r="K144">
-        <v>314000000</v>
+        <v>170000000</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="B145">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C145" t="s">
-        <v>6</v>
-      </c>
-      <c r="D145">
-        <v>10245000000</v>
+        <v>13</v>
       </c>
       <c r="E145">
-        <v>8501000000</v>
-      </c>
-      <c r="F145">
-        <v>9052000000</v>
-      </c>
-      <c r="G145">
-        <v>572000000</v>
+        <v>5230000000</v>
       </c>
       <c r="H145">
-        <v>51180000000</v>
+        <v>32889000000</v>
       </c>
       <c r="I145">
-        <v>60060000000</v>
-      </c>
-      <c r="J145">
-        <v>6295000000</v>
+        <v>39379000000</v>
       </c>
       <c r="K145">
-        <v>262000000</v>
+        <v>144000000</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C146" t="s">
-        <v>6</v>
-      </c>
-      <c r="D146">
-        <v>9251000000</v>
+        <v>13</v>
       </c>
       <c r="E146">
-        <v>7762000000</v>
-      </c>
-      <c r="F146">
-        <v>7711000000</v>
-      </c>
-      <c r="G146">
-        <v>946000000</v>
+        <v>5314000000</v>
       </c>
       <c r="H146">
-        <v>47725000000</v>
+        <v>33224000000</v>
       </c>
       <c r="I146">
-        <v>58145000000</v>
+        <v>40004000000</v>
       </c>
       <c r="K146">
-        <v>272000000</v>
+        <v>264000000</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="B147">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C147" t="s">
-        <v>6</v>
-      </c>
-      <c r="D147">
-        <v>10447000000</v>
+        <v>13</v>
       </c>
       <c r="E147">
-        <v>8970000000</v>
-      </c>
-      <c r="F147">
-        <v>8024000000</v>
-      </c>
-      <c r="G147">
-        <v>1546000000</v>
+        <v>3845000000</v>
       </c>
       <c r="H147">
-        <v>56415000000</v>
+        <v>23935000000</v>
       </c>
       <c r="I147">
-        <v>65979000000</v>
+        <v>35350000000</v>
       </c>
       <c r="K147">
-        <v>324000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="B148">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C148" t="s">
-        <v>6</v>
-      </c>
-      <c r="D148">
-        <v>10483000000</v>
+        <v>13</v>
       </c>
       <c r="E148">
-        <v>9071000000</v>
-      </c>
-      <c r="F148">
-        <v>8514000000</v>
-      </c>
-      <c r="G148">
-        <v>1259000000</v>
+        <v>704000000</v>
       </c>
       <c r="H148">
-        <v>58973000000</v>
+        <v>5614000000</v>
       </c>
       <c r="I148">
-        <v>69028000000</v>
+        <v>17887000000</v>
       </c>
       <c r="K148">
-        <v>326000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="B149">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C149" t="s">
-        <v>6</v>
-      </c>
-      <c r="D149">
-        <v>9458000000</v>
+        <v>13</v>
       </c>
       <c r="E149">
-        <v>7974000000</v>
-      </c>
-      <c r="F149">
-        <v>8438000000</v>
-      </c>
-      <c r="G149">
-        <v>622000000</v>
+        <v>1454000000</v>
       </c>
       <c r="H149">
-        <v>49985000000</v>
+        <v>11888000000</v>
       </c>
       <c r="I149">
-        <v>58715000000</v>
-      </c>
-      <c r="J149">
-        <v>5999000000</v>
+        <v>26464000000</v>
       </c>
       <c r="K149">
-        <v>193000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="B150">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C150" t="s">
-        <v>6</v>
-      </c>
-      <c r="D150">
-        <v>9388000000</v>
+        <v>13</v>
       </c>
       <c r="E150">
-        <v>7923000000</v>
-      </c>
-      <c r="F150">
-        <v>7990000000</v>
-      </c>
-      <c r="G150">
-        <v>746000000</v>
+        <v>1663000000</v>
       </c>
       <c r="H150">
-        <v>46221000000</v>
+        <v>12784000000</v>
       </c>
       <c r="I150">
-        <v>56597000000</v>
+        <v>23756000000</v>
       </c>
       <c r="K150">
-        <v>136000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="B151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C151" t="s">
-        <v>6</v>
-      </c>
-      <c r="D151">
-        <v>10707000000</v>
+        <v>13</v>
       </c>
       <c r="E151">
-        <v>9139000000</v>
-      </c>
-      <c r="F151">
-        <v>8233000000</v>
-      </c>
-      <c r="G151">
-        <v>1485000000</v>
+        <v>1712000000</v>
       </c>
       <c r="H151">
-        <v>54755000000</v>
+        <v>14875000000</v>
       </c>
       <c r="I151">
-        <v>63937000000</v>
+        <v>23146000000</v>
       </c>
       <c r="K151">
-        <v>411000000</v>
+        <v>24000000</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="B152">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C152" t="s">
-        <v>6</v>
-      </c>
-      <c r="D152">
-        <v>11107000000</v>
+        <v>13</v>
       </c>
       <c r="E152">
-        <v>9595000000</v>
-      </c>
-      <c r="F152">
-        <v>8894000000</v>
-      </c>
-      <c r="G152">
-        <v>1315000000</v>
+        <v>3569000000</v>
       </c>
       <c r="H152">
-        <v>59076000000</v>
+        <v>27689000000</v>
       </c>
       <c r="I152">
-        <v>68031000000</v>
+        <v>33414000000</v>
       </c>
       <c r="K152">
-        <v>563000000</v>
+        <v>85000000</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="B153">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C153" t="s">
-        <v>6</v>
-      </c>
-      <c r="D153">
-        <v>9502000000</v>
+        <v>13</v>
       </c>
       <c r="E153">
-        <v>8125000000</v>
-      </c>
-      <c r="F153">
-        <v>7785000000</v>
-      </c>
-      <c r="G153">
-        <v>980000000</v>
+        <v>4227000000</v>
       </c>
       <c r="H153">
-        <v>49573000000</v>
+        <v>31285000000</v>
       </c>
       <c r="I153">
-        <v>58199000000</v>
-      </c>
-      <c r="J153">
-        <v>6531000000</v>
+        <v>38756000000</v>
       </c>
       <c r="K153">
-        <v>380000000</v>
+        <v>77000000</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="B154">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C154" t="s">
-        <v>6</v>
-      </c>
-      <c r="D154">
-        <v>8916000000</v>
+        <v>13</v>
       </c>
       <c r="E154">
-        <v>7677000000</v>
-      </c>
-      <c r="F154">
-        <v>8296000000</v>
-      </c>
-      <c r="G154">
-        <v>213000000</v>
+        <v>4557000000</v>
       </c>
       <c r="H154">
-        <v>44601000000</v>
+        <v>29713000000</v>
       </c>
       <c r="I154">
-        <v>53904000000</v>
+        <v>36690000000</v>
       </c>
       <c r="K154">
-        <v>99000000</v>
+        <v>43000000</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="B155">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C155" t="s">
-        <v>6</v>
-      </c>
-      <c r="D155">
-        <v>10621000000</v>
+        <v>13</v>
       </c>
       <c r="E155">
-        <v>9266000000</v>
-      </c>
-      <c r="F155">
-        <v>9042000000</v>
-      </c>
-      <c r="G155">
-        <v>801000000</v>
+        <v>4135000000</v>
       </c>
       <c r="H155">
-        <v>53341000000</v>
+        <v>26483000000</v>
       </c>
       <c r="I155">
-        <v>61817000000</v>
+        <v>34384000000</v>
       </c>
       <c r="K155">
-        <v>340000000</v>
+        <v>37000000</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="B156">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C156" t="s">
-        <v>6</v>
-      </c>
-      <c r="D156">
-        <v>11178000000</v>
+        <v>13</v>
       </c>
       <c r="E156">
-        <v>9776000000</v>
-      </c>
-      <c r="F156">
-        <v>10343000000</v>
-      </c>
-      <c r="G156">
-        <v>357000000</v>
+        <v>6119000000</v>
       </c>
       <c r="H156">
-        <v>56955000000</v>
+        <v>32523000000</v>
       </c>
       <c r="I156">
-        <v>65926000000</v>
+        <v>37322000000</v>
       </c>
       <c r="K156">
-        <v>384000000</v>
+        <v>81000000</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="B157">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C157" t="s">
-        <v>6</v>
-      </c>
-      <c r="D157">
-        <v>9647000000</v>
+        <v>13</v>
       </c>
       <c r="E157">
-        <v>8235000000</v>
-      </c>
-      <c r="F157">
-        <v>10475000000</v>
-      </c>
-      <c r="G157">
-        <v>-712000000</v>
+        <v>5613000000</v>
       </c>
       <c r="H157">
-        <v>48028000000</v>
+        <v>33534000000</v>
       </c>
       <c r="I157">
-        <v>58029000000</v>
-      </c>
-      <c r="J157">
-        <v>8188000000</v>
+        <v>39272000000</v>
       </c>
       <c r="K157">
-        <v>262000000</v>
+        <v>57000000</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="B158">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C158" t="s">
-        <v>7</v>
-      </c>
-      <c r="D158">
-        <v>8420000000</v>
+        <v>13</v>
       </c>
       <c r="E158">
-        <v>7174000000</v>
-      </c>
-      <c r="F158">
-        <v>8142000000</v>
-      </c>
-      <c r="G158">
-        <v>96000000</v>
+        <v>5541000000</v>
       </c>
       <c r="H158">
-        <v>47611000000</v>
+        <v>31303000000</v>
       </c>
       <c r="I158">
-        <v>59808000000</v>
+        <v>37490000000</v>
       </c>
       <c r="K158">
-        <v>28000000</v>
+        <v>49000000</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="B159">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C159" t="s">
-        <v>7</v>
-      </c>
-      <c r="D159">
-        <v>10000000000</v>
+        <v>13</v>
       </c>
       <c r="E159">
-        <v>8622000000</v>
-      </c>
-      <c r="F159">
-        <v>8601000000</v>
-      </c>
-      <c r="G159">
-        <v>818000000</v>
+        <v>5105000000</v>
       </c>
       <c r="H159">
-        <v>56356000000</v>
+        <v>29547000000</v>
       </c>
       <c r="I159">
-        <v>67467000000</v>
+        <v>38062000000</v>
       </c>
       <c r="K159">
-        <v>140000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="B160">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C160" t="s">
-        <v>7</v>
-      </c>
-      <c r="D160">
-        <v>9878000000</v>
+        <v>13</v>
       </c>
       <c r="E160">
-        <v>8528000000</v>
-      </c>
-      <c r="F160">
-        <v>8786000000</v>
-      </c>
-      <c r="G160">
-        <v>637000000</v>
+        <v>6409000000</v>
       </c>
       <c r="H160">
-        <v>59145000000</v>
+        <v>35505000000</v>
       </c>
       <c r="I160">
-        <v>70083000000</v>
+        <v>42579000000</v>
       </c>
       <c r="K160">
-        <v>109000000</v>
+        <v>121000000</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="B161">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C161" t="s">
-        <v>7</v>
-      </c>
-      <c r="D161">
-        <v>9438000000</v>
+        <v>13</v>
       </c>
       <c r="E161">
-        <v>8080000000</v>
-      </c>
-      <c r="F161">
-        <v>8709000000</v>
-      </c>
-      <c r="G161">
-        <v>580000000</v>
+        <v>5912000000</v>
       </c>
       <c r="H161">
-        <v>53149000000</v>
+        <v>35624000000</v>
       </c>
       <c r="I161">
-        <v>65028000000</v>
-      </c>
-      <c r="J161">
-        <v>11703000000</v>
+        <v>44169000000</v>
       </c>
       <c r="K161">
-        <v>73000000</v>
+        <v>38000000</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="B162">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C162" t="s">
-        <v>7</v>
-      </c>
-      <c r="D162">
-        <v>8195000000</v>
+        <v>13</v>
       </c>
       <c r="E162">
-        <v>6990000000</v>
-      </c>
-      <c r="F162">
-        <v>7546000000</v>
-      </c>
-      <c r="G162">
-        <v>313000000</v>
+        <v>6211000000</v>
       </c>
       <c r="H162">
-        <v>46582000000</v>
+        <v>35580000000</v>
       </c>
       <c r="I162">
-        <v>58273000000</v>
+        <v>45513000000</v>
       </c>
       <c r="K162">
-        <v>94000000</v>
+        <v>41000000</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="B163">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C163" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D163">
-        <v>9396000000</v>
+        <v>6870000000</v>
       </c>
       <c r="E163">
-        <v>8103000000</v>
+        <v>6250000000</v>
       </c>
       <c r="F163">
-        <v>8336000000</v>
+        <v>6832000000</v>
       </c>
       <c r="G163">
-        <v>588000000</v>
+        <v>67000000</v>
       </c>
       <c r="H163">
-        <v>54017000000</v>
+        <v>36735000000</v>
       </c>
       <c r="I163">
-        <v>64725000000</v>
+        <v>45219000000</v>
+      </c>
+      <c r="J163">
+        <v>5075000000</v>
       </c>
       <c r="K163">
-        <v>153000000</v>
+        <v>18000000</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="B164">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C164" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D164">
-        <v>9913000000</v>
+        <v>7354000000</v>
       </c>
       <c r="E164">
-        <v>8603000000</v>
+        <v>6712000000</v>
       </c>
       <c r="F164">
-        <v>8289000000</v>
+        <v>6956000000</v>
       </c>
       <c r="G164">
-        <v>965000000</v>
+        <v>367000000</v>
       </c>
       <c r="H164">
-        <v>58172000000</v>
+        <v>38221000000</v>
       </c>
       <c r="I164">
-        <v>68074000000</v>
+        <v>46250000000</v>
+      </c>
+      <c r="J164">
+        <v>5065000000</v>
       </c>
       <c r="K164">
-        <v>235000000</v>
+        <v>31000000</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="B165">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C165" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D165">
-        <v>9052000000</v>
+        <v>6329000000</v>
       </c>
       <c r="E165">
-        <v>7761000000</v>
+        <v>5712000000</v>
       </c>
       <c r="F165">
-        <v>8047000000</v>
+        <v>6722000000</v>
       </c>
       <c r="G165">
-        <v>397000000</v>
+        <v>-231000000</v>
       </c>
       <c r="H165">
-        <v>51538000000</v>
+        <v>33087000000</v>
       </c>
       <c r="I165">
-        <v>62518000000</v>
+        <v>42248000000</v>
       </c>
       <c r="J165">
-        <v>9918000000</v>
+        <v>7974000000</v>
       </c>
       <c r="K165">
-        <v>145000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B166">
         <v>1</v>
       </c>
       <c r="C166" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D166">
-        <v>8608000000</v>
+        <v>9624000000</v>
       </c>
       <c r="E166">
-        <v>7420000000</v>
+        <v>8155000000</v>
       </c>
       <c r="F166">
-        <v>7867000000</v>
+        <v>9023000000</v>
       </c>
       <c r="G166">
-        <v>508000000</v>
+        <v>234000000</v>
       </c>
       <c r="H166">
-        <v>46444000000</v>
+        <v>50984000000</v>
       </c>
       <c r="I166">
-        <v>57269000000</v>
+        <v>64341000000</v>
+      </c>
+      <c r="J166">
+        <v>22829000000</v>
       </c>
       <c r="K166">
-        <v>100000000</v>
+        <v>31000000</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B167">
         <v>2</v>
       </c>
       <c r="C167" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D167">
-        <v>9914000000</v>
+        <v>11105000000</v>
       </c>
       <c r="E167">
-        <v>8676000000</v>
+        <v>9582000000</v>
       </c>
       <c r="F167">
-        <v>8469000000</v>
+        <v>9570000000</v>
       </c>
       <c r="G167">
-        <v>1193000000</v>
+        <v>803000000</v>
       </c>
       <c r="H167">
-        <v>54289000000</v>
+        <v>59564000000</v>
       </c>
       <c r="I167">
-        <v>64685000000</v>
+        <v>71743000000</v>
+      </c>
+      <c r="J167">
+        <v>22525000000</v>
       </c>
       <c r="K167">
-        <v>195000000</v>
+        <v>94000000</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B168">
         <v>3</v>
       </c>
       <c r="C168" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D168">
-        <v>10306000000</v>
+        <v>10878000000</v>
       </c>
       <c r="E168">
-        <v>8960000000</v>
+        <v>9377000000</v>
       </c>
       <c r="F168">
-        <v>8407000000</v>
+        <v>9646000000</v>
       </c>
       <c r="G168">
-        <v>4816000000</v>
+        <v>624000000</v>
       </c>
       <c r="H168">
-        <v>57160000000</v>
+        <v>54012000000</v>
       </c>
       <c r="I168">
-        <v>66745000000</v>
+        <v>64582000000</v>
+      </c>
+      <c r="J168">
+        <v>22217000000</v>
       </c>
       <c r="K168">
-        <v>257000000</v>
+        <v>70000000</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B169">
         <v>4</v>
       </c>
       <c r="C169" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D169">
-        <v>9036000000</v>
+        <v>10600000000</v>
       </c>
       <c r="E169">
-        <v>7729000000</v>
+        <v>9019000000</v>
       </c>
       <c r="F169">
-        <v>7955000000</v>
+        <v>9910000000</v>
       </c>
       <c r="G169">
-        <v>823000000</v>
+        <v>258000000</v>
       </c>
       <c r="H169">
-        <v>50718000000</v>
+        <v>55327000000</v>
       </c>
       <c r="I169">
-        <v>61304000000</v>
+        <v>67355000000</v>
       </c>
       <c r="J169">
-        <v>9673000000</v>
+        <v>22511000000</v>
       </c>
       <c r="K169">
-        <v>146000000</v>
+        <v>47000000</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="B170">
         <v>1</v>
       </c>
       <c r="C170" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D170">
-        <v>8696000000</v>
+        <v>9435000000</v>
       </c>
       <c r="E170">
-        <v>7384000000</v>
+        <v>8087000000</v>
       </c>
       <c r="F170">
-        <v>9045000000</v>
+        <v>8100000000</v>
       </c>
       <c r="G170">
-        <v>-609000000</v>
+        <v>700000000</v>
       </c>
       <c r="H170">
-        <v>46383000000</v>
+        <v>51771000000</v>
       </c>
       <c r="I170">
-        <v>57216000000</v>
+        <v>65064000000</v>
+      </c>
+      <c r="J170">
+        <v>19134000000</v>
       </c>
       <c r="K170">
-        <v>0</v>
+        <v>73000000</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="B171">
         <v>2</v>
       </c>
       <c r="C171" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D171">
-        <v>10329000000</v>
+        <v>10363000000</v>
       </c>
       <c r="E171">
-        <v>8981000000</v>
+        <v>8995000000</v>
       </c>
       <c r="F171">
-        <v>9423000000</v>
+        <v>8612000000</v>
       </c>
       <c r="G171">
-        <v>789000000</v>
+        <v>950000000</v>
       </c>
       <c r="H171">
-        <v>53900000000</v>
+        <v>58336000000</v>
       </c>
       <c r="I171">
-        <v>63214000000</v>
+        <v>70751000000</v>
+      </c>
+      <c r="J171">
+        <v>21131000000</v>
       </c>
       <c r="K171">
-        <v>78000000</v>
+        <v>98000000</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="B172">
         <v>3</v>
       </c>
       <c r="C172" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D172">
-        <v>10563000000</v>
+        <v>10594000000</v>
       </c>
       <c r="E172">
-        <v>9314000000</v>
+        <v>9150000000</v>
       </c>
       <c r="F172">
-        <v>9372000000</v>
+        <v>9163000000</v>
       </c>
       <c r="G172">
-        <v>924000000</v>
+        <v>737000000</v>
       </c>
       <c r="H172">
-        <v>56065000000</v>
+        <v>53472000000</v>
       </c>
       <c r="I172">
-        <v>65378000000</v>
+        <v>63751000000</v>
+      </c>
+      <c r="J172">
+        <v>21545000000</v>
       </c>
       <c r="K172">
-        <v>103000000</v>
+        <v>86000000</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="B173">
         <v>4</v>
       </c>
       <c r="C173" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D173">
-        <v>9313000000</v>
+        <v>9789000000</v>
       </c>
       <c r="E173">
-        <v>8083000000</v>
+        <v>8347000000</v>
       </c>
       <c r="F173">
-        <v>8688000000</v>
+        <v>9022000000</v>
       </c>
       <c r="G173">
-        <v>28000000</v>
+        <v>289000000</v>
       </c>
       <c r="H173">
-        <v>49211000000</v>
+        <v>53452000000</v>
       </c>
       <c r="I173">
-        <v>60213000000</v>
+        <v>65683000000</v>
       </c>
       <c r="J173">
-        <v>9953000000</v>
+        <v>22489000000</v>
       </c>
       <c r="K173">
-        <v>54000000</v>
+        <v>57000000</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="B174">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C174" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D174">
-        <v>15559000000</v>
+        <v>9827000000</v>
       </c>
       <c r="E174">
-        <v>12815000000</v>
+        <v>8441000000</v>
       </c>
       <c r="F174">
-        <v>13842000000</v>
+        <v>8611000000</v>
       </c>
       <c r="G174">
-        <v>843000000</v>
+        <v>932000000</v>
       </c>
       <c r="H174">
-        <v>60387000000</v>
+        <v>50190000000</v>
       </c>
       <c r="I174">
-        <v>72035000000</v>
+        <v>62791000000</v>
       </c>
       <c r="J174">
-        <v>13546000000</v>
+        <v>17638000000</v>
       </c>
       <c r="K174">
-        <v>425000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>2024</v>
-      </c>
-      <c r="B175" t="s">
-        <v>8</v>
+        <v>2015</v>
+      </c>
+      <c r="B175">
+        <v>2</v>
       </c>
       <c r="C175" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D175">
-        <v>61643000000</v>
+        <v>10827000000</v>
       </c>
       <c r="E175">
-        <v>50894000000</v>
+        <v>9414000000</v>
       </c>
       <c r="F175">
-        <v>55648000000</v>
+        <v>8906000000</v>
       </c>
       <c r="G175">
-        <v>3457000000</v>
+        <v>1704000000</v>
       </c>
       <c r="H175">
-        <v>246145000000</v>
+        <v>57821000000</v>
       </c>
       <c r="I175">
-        <v>288394000000</v>
+        <v>69401000000</v>
       </c>
       <c r="J175">
-        <v>13546000000</v>
+        <v>17152000000</v>
       </c>
       <c r="K175">
-        <v>1389000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="B176">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C176" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D176">
-        <v>14695000000</v>
+        <v>10706000000</v>
       </c>
       <c r="E176">
-        <v>13275000000</v>
+        <v>9353000000</v>
       </c>
       <c r="F176">
-        <v>13192000000</v>
+        <v>8707000000</v>
       </c>
       <c r="G176">
-        <v>985000000</v>
+        <v>1693000000</v>
       </c>
       <c r="H176">
-        <v>64463000000</v>
+        <v>60866000000</v>
       </c>
       <c r="I176">
-        <v>78298000000</v>
+        <v>71092000000</v>
       </c>
       <c r="J176">
-        <v>21680000000</v>
+        <v>18849000000</v>
       </c>
       <c r="K176">
-        <v>294000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>2024</v>
-      </c>
-      <c r="B177" t="s">
-        <v>8</v>
+        <v>2015</v>
+      </c>
+      <c r="B177">
+        <v>4</v>
       </c>
       <c r="C177" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D177">
-        <v>57063000000</v>
+        <v>9630000000</v>
       </c>
       <c r="E177">
-        <v>51829000000</v>
+        <v>8305000000</v>
       </c>
       <c r="F177">
-        <v>51967000000</v>
+        <v>8562000000</v>
       </c>
       <c r="G177">
-        <v>3149000000</v>
+        <v>3281000000</v>
       </c>
       <c r="H177">
-        <v>258503000000</v>
+        <v>54133000000</v>
       </c>
       <c r="I177">
-        <v>311185000000</v>
+        <v>65453000000</v>
       </c>
       <c r="J177">
-        <v>21680000000</v>
+        <v>18330000000</v>
       </c>
       <c r="K177">
-        <v>713000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="B178">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C178" t="s">
         <v>5</v>
       </c>
       <c r="D178">
-        <v>13660000000</v>
+        <v>9995000000</v>
       </c>
       <c r="E178">
-        <v>12402000000</v>
+        <v>8665000000</v>
       </c>
       <c r="F178">
-        <v>12526000000</v>
+        <v>9265000000</v>
       </c>
       <c r="G178">
-        <v>590000000</v>
+        <v>480000000</v>
       </c>
       <c r="H178">
-        <v>60676000000</v>
+        <v>50886000000</v>
       </c>
       <c r="I178">
-        <v>71503000000</v>
+        <v>63392000000</v>
       </c>
       <c r="J178">
-        <v>24617000000</v>
+        <v>15244000000</v>
       </c>
       <c r="K178">
-        <f>ROUND($K$179*((D178-F178)/($D$179-$F$179)),0)</f>
-        <v>98910482</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>2024</v>
-      </c>
-      <c r="B179" t="s">
-        <v>8</v>
+        <v>2014</v>
+      </c>
+      <c r="B179">
+        <v>2</v>
       </c>
       <c r="C179" t="s">
         <v>5</v>
       </c>
       <c r="D179">
-        <v>54211000000</v>
+        <v>11355000000</v>
       </c>
       <c r="E179">
-        <v>49586000000</v>
+        <v>9920000000</v>
       </c>
       <c r="F179">
-        <v>51597000000</v>
+        <v>9956000000</v>
       </c>
       <c r="G179">
-        <v>846000000</v>
+        <v>864000000</v>
       </c>
       <c r="H179">
-        <v>248795000000</v>
+        <v>57194000000</v>
       </c>
       <c r="I179">
-        <v>292948000000</v>
+        <v>68090000000</v>
       </c>
       <c r="J179">
-        <v>24617000000</v>
+        <v>15205000000</v>
       </c>
       <c r="K179">
-        <v>228000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="B180">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C180" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D180">
-        <v>6931000000</v>
+        <v>11139000000</v>
       </c>
       <c r="E180">
-        <v>6307000000</v>
+        <v>9758000000</v>
       </c>
       <c r="F180">
-        <v>6653000000</v>
+        <v>9879000000</v>
       </c>
       <c r="G180">
-        <v>261000000</v>
+        <v>942000000</v>
       </c>
       <c r="H180">
-        <v>34471000000</v>
+        <v>57650000000</v>
       </c>
       <c r="I180">
-        <v>43533000000</v>
+        <v>69120000000</v>
       </c>
       <c r="J180">
-        <v>5069000000</v>
+        <v>15651000000</v>
       </c>
       <c r="K180">
-        <v>54000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>2024</v>
-      </c>
-      <c r="B181" t="s">
-        <v>8</v>
+        <v>2014</v>
+      </c>
+      <c r="B181">
+        <v>4</v>
       </c>
       <c r="C181" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D181">
-        <v>27483000000</v>
+        <v>10160000000</v>
       </c>
       <c r="E181">
-        <v>24980000000</v>
+        <v>8782000000</v>
       </c>
       <c r="F181">
-        <v>27162000000</v>
+        <v>9300000000</v>
       </c>
       <c r="G181">
-        <v>465000000</v>
+        <v>597000000</v>
       </c>
       <c r="H181">
-        <v>142515000000</v>
+        <v>52140000000</v>
       </c>
       <c r="I181">
-        <v>177250000000</v>
+        <v>65053000000</v>
       </c>
       <c r="J181">
-        <v>5069000000</v>
+        <v>16196000000</v>
       </c>
       <c r="K181">
-        <v>103000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -7184,862 +6779,816 @@
         <v>6</v>
       </c>
       <c r="D182">
-        <v>14040000000</v>
+        <v>9148000000</v>
       </c>
       <c r="E182">
-        <v>11480000000</v>
+        <v>7688000000</v>
       </c>
       <c r="F182">
-        <v>13471000000</v>
+        <v>8095000000</v>
       </c>
       <c r="G182">
-        <v>240000000</v>
+        <v>603000000</v>
       </c>
       <c r="H182">
-        <v>55678000000</v>
+        <v>47952000000</v>
       </c>
       <c r="I182">
-        <v>68401000000</v>
-      </c>
-      <c r="J182">
-        <v>12432000000</v>
+        <v>57871000000</v>
       </c>
       <c r="K182">
-        <v>124000000</v>
+        <v>151000000</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="B183">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C183" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D183">
-        <v>13213000000</v>
+        <v>10791000000</v>
       </c>
       <c r="E183">
-        <v>11860000000</v>
+        <v>9231000000</v>
       </c>
       <c r="F183">
-        <v>12605000000</v>
+        <v>8763000000</v>
       </c>
       <c r="G183">
-        <v>387000000</v>
+        <v>1224000000</v>
       </c>
       <c r="H183">
-        <v>59517000000</v>
+        <v>57575000000</v>
       </c>
       <c r="I183">
-        <v>75155000000</v>
+        <v>66227000000</v>
       </c>
       <c r="K183">
-        <v>43000000</v>
+        <v>338000000</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="B184">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C184" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D184">
-        <v>12551000000</v>
+        <v>11060000000</v>
       </c>
       <c r="E184">
-        <v>11391000000</v>
+        <v>9399000000</v>
       </c>
       <c r="F184">
-        <v>12821000000</v>
+        <v>9221000000</v>
       </c>
       <c r="G184">
-        <v>-473000000</v>
+        <v>1178000000</v>
       </c>
       <c r="H184">
-        <v>56356000000</v>
+        <v>61006000000</v>
       </c>
       <c r="I184">
-        <v>69904000000</v>
-      </c>
-      <c r="J184">
-        <v>24705000000</v>
+        <v>70167000000</v>
       </c>
       <c r="K184">
-        <v>0</v>
+        <v>314000000</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="B185">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C185" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D185">
-        <v>6428000000</v>
+        <v>10245000000</v>
       </c>
       <c r="E185">
-        <v>5811000000</v>
+        <v>8501000000</v>
       </c>
       <c r="F185">
-        <v>6651000000</v>
+        <v>9052000000</v>
       </c>
       <c r="G185">
-        <v>-149000000</v>
+        <v>572000000</v>
       </c>
       <c r="H185">
-        <v>30629000000</v>
+        <v>51180000000</v>
       </c>
       <c r="I185">
-        <v>41432000000</v>
+        <v>60060000000</v>
       </c>
       <c r="J185">
-        <v>4086000000</v>
+        <v>6295000000</v>
       </c>
       <c r="K185">
-        <v>0</v>
+        <v>262000000</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>2025</v>
+        <v>2016</v>
       </c>
       <c r="B186">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C186" t="s">
         <v>6</v>
       </c>
       <c r="D186">
-        <v>16648000000</v>
+        <v>9251000000</v>
       </c>
       <c r="E186">
-        <v>13867000000</v>
+        <v>7762000000</v>
       </c>
       <c r="F186">
-        <v>14546000000</v>
+        <v>7711000000</v>
       </c>
       <c r="G186">
-        <v>2130000000</v>
+        <v>946000000</v>
       </c>
       <c r="H186">
-        <v>66417000000</v>
+        <v>47725000000</v>
       </c>
       <c r="I186">
-        <v>77645000000</v>
-      </c>
-      <c r="J186">
-        <v>12400000000</v>
+        <v>58145000000</v>
       </c>
       <c r="K186">
-        <v>470000000</v>
+        <v>272000000</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>2025</v>
+        <v>2016</v>
       </c>
       <c r="B187">
         <v>2</v>
       </c>
       <c r="C187" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D187">
-        <v>15236000000</v>
+        <v>10447000000</v>
       </c>
       <c r="E187">
-        <v>13836000000</v>
+        <v>8970000000</v>
       </c>
       <c r="F187">
-        <v>13911000000</v>
+        <v>8024000000</v>
       </c>
       <c r="G187">
-        <v>973000000</v>
+        <v>1546000000</v>
       </c>
       <c r="H187">
-        <v>70088000000</v>
+        <v>56415000000</v>
       </c>
       <c r="I187">
-        <v>84347000000</v>
+        <v>65979000000</v>
       </c>
       <c r="K187">
-        <v>188000000</v>
+        <v>324000000</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>2025</v>
+        <v>2016</v>
       </c>
       <c r="B188">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C188" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D188">
-        <v>14392000000</v>
+        <v>10483000000</v>
       </c>
       <c r="E188">
-        <v>13123000000</v>
+        <v>9071000000</v>
       </c>
       <c r="F188">
-        <v>13257000000</v>
+        <v>8514000000</v>
       </c>
       <c r="G188">
-        <v>599000000</v>
+        <v>1259000000</v>
       </c>
       <c r="H188">
-        <v>65762000000</v>
+        <v>58973000000</v>
       </c>
       <c r="I188">
-        <v>77636000000</v>
-      </c>
-      <c r="J188">
-        <v>24217000000</v>
+        <v>69028000000</v>
       </c>
       <c r="K188">
-        <v>41000000</v>
+        <v>326000000</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>2025</v>
+        <v>2016</v>
       </c>
       <c r="B189">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C189" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D189">
-        <v>7244000000</v>
+        <v>9458000000</v>
       </c>
       <c r="E189">
-        <v>6627000000</v>
+        <v>7974000000</v>
       </c>
       <c r="F189">
-        <v>7019000000</v>
+        <v>8438000000</v>
       </c>
       <c r="G189">
-        <v>213000000</v>
+        <v>622000000</v>
       </c>
       <c r="H189">
-        <v>36885000000</v>
+        <v>49985000000</v>
       </c>
       <c r="I189">
-        <v>46996000000</v>
+        <v>58715000000</v>
       </c>
       <c r="J189">
-        <v>4081000000</v>
+        <v>5999000000</v>
       </c>
       <c r="K189">
-        <v>14000000</v>
+        <v>193000000</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>2025</v>
+        <v>2015</v>
       </c>
       <c r="B190">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C190" t="s">
         <v>6</v>
       </c>
       <c r="D190">
-        <v>16673000000</v>
+        <v>9388000000</v>
       </c>
       <c r="E190">
-        <v>13506000000</v>
+        <v>7923000000</v>
       </c>
       <c r="F190">
-        <v>14989000000</v>
+        <v>7990000000</v>
       </c>
       <c r="G190">
-        <v>1417000000</v>
+        <v>746000000</v>
       </c>
       <c r="H190">
-        <v>67621000000</v>
+        <v>46221000000</v>
       </c>
       <c r="I190">
-        <v>79054000000</v>
-      </c>
-      <c r="J190">
-        <v>12299000000</v>
+        <v>56597000000</v>
       </c>
       <c r="K190">
-        <v>392000000</v>
+        <v>136000000</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>2025</v>
+        <v>2015</v>
       </c>
       <c r="B191">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C191" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D191">
-        <v>15225000000</v>
+        <v>10707000000</v>
       </c>
       <c r="E191">
-        <v>13815000000</v>
+        <v>9139000000</v>
       </c>
       <c r="F191">
-        <v>13830000000</v>
+        <v>8233000000</v>
       </c>
       <c r="G191">
-        <v>949000000</v>
+        <v>1485000000</v>
       </c>
       <c r="H191">
-        <v>73769000000</v>
+        <v>54755000000</v>
       </c>
       <c r="I191">
-        <v>87417000000</v>
+        <v>63937000000</v>
       </c>
       <c r="K191">
-        <v>228000000</v>
+        <v>411000000</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>2025</v>
+        <v>2015</v>
       </c>
       <c r="B192">
         <v>3</v>
       </c>
       <c r="C192" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D192">
-        <v>13691000000</v>
+        <v>11107000000</v>
       </c>
       <c r="E192">
-        <v>12471000000</v>
+        <v>9595000000</v>
       </c>
       <c r="F192">
-        <v>13540000000</v>
+        <v>8894000000</v>
       </c>
       <c r="G192">
-        <v>-114000000</v>
+        <v>1315000000</v>
       </c>
       <c r="H192">
-        <v>66580000000</v>
+        <v>59076000000</v>
       </c>
       <c r="I192">
-        <v>77400000000</v>
-      </c>
-      <c r="J192">
-        <v>24538000000</v>
+        <v>68031000000</v>
       </c>
       <c r="K192">
-        <v>0</v>
+        <v>563000000</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>2025</v>
+        <v>2015</v>
       </c>
       <c r="B193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C193" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D193">
-        <v>6949000000</v>
+        <v>9502000000</v>
       </c>
       <c r="E193">
-        <v>6313000000</v>
+        <v>8125000000</v>
       </c>
       <c r="F193">
-        <v>6914000000</v>
+        <v>7785000000</v>
       </c>
       <c r="G193">
-        <v>54000000</v>
+        <v>980000000</v>
       </c>
       <c r="H193">
-        <v>36362000000</v>
+        <v>49573000000</v>
       </c>
       <c r="I193">
-        <v>45567000000</v>
+        <v>58199000000</v>
       </c>
       <c r="J193">
-        <v>4079000000</v>
+        <v>6531000000</v>
       </c>
       <c r="K193">
-        <v>11000000</v>
+        <v>380000000</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="B194">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C194" t="s">
         <v>6</v>
       </c>
       <c r="D194">
-        <v>16003000000</v>
+        <v>8916000000</v>
       </c>
       <c r="E194">
-        <v>12916000000</v>
+        <v>7677000000</v>
       </c>
       <c r="F194">
-        <v>14536000000</v>
+        <v>8296000000</v>
       </c>
       <c r="G194">
-        <v>1219000000</v>
+        <v>213000000</v>
       </c>
       <c r="H194">
-        <v>59861000000</v>
+        <v>44601000000</v>
       </c>
       <c r="I194">
-        <v>72946000000</v>
-      </c>
-      <c r="J194">
-        <v>11936000000</v>
+        <v>53904000000</v>
       </c>
       <c r="K194">
-        <v>351000000</v>
+        <v>99000000</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>2025</v>
-      </c>
-      <c r="B195" t="s">
-        <v>8</v>
+        <v>2014</v>
+      </c>
+      <c r="B195">
+        <v>2</v>
       </c>
       <c r="C195" t="s">
         <v>6</v>
       </c>
       <c r="D195">
-        <v>63364000000</v>
+        <v>10621000000</v>
       </c>
       <c r="E195">
-        <v>51768000000</v>
+        <v>9266000000</v>
       </c>
       <c r="F195">
-        <v>57542000000</v>
+        <v>9042000000</v>
       </c>
       <c r="G195">
-        <v>5005000000</v>
+        <v>801000000</v>
       </c>
       <c r="H195">
-        <v>249578000000</v>
+        <v>53341000000</v>
       </c>
       <c r="I195">
-        <v>298045000000</v>
-      </c>
-      <c r="J195">
-        <v>11936000000</v>
+        <v>61817000000</v>
       </c>
       <c r="K195">
-        <v>1337000000</v>
+        <v>340000000</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="B196">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C196" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D196">
-        <v>15397000000</v>
+        <v>11178000000</v>
       </c>
       <c r="E196">
-        <v>13926000000</v>
+        <v>9776000000</v>
       </c>
       <c r="F196">
-        <v>14011000000</v>
+        <v>10343000000</v>
       </c>
       <c r="G196">
-        <v>1044000000</v>
+        <v>357000000</v>
       </c>
       <c r="H196">
-        <v>68246000000</v>
+        <v>56955000000</v>
       </c>
       <c r="I196">
-        <v>83365000000</v>
-      </c>
-      <c r="J196">
-        <v>17170000000</v>
+        <v>65926000000</v>
       </c>
       <c r="K196">
-        <v>244000000</v>
+        <v>384000000</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>2025</v>
-      </c>
-      <c r="B197" t="s">
-        <v>8</v>
+        <v>2014</v>
+      </c>
+      <c r="B197">
+        <v>4</v>
       </c>
       <c r="C197" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D197">
-        <v>59070000000</v>
+        <v>9647000000</v>
       </c>
       <c r="E197">
-        <v>53438000000</v>
+        <v>8235000000</v>
       </c>
       <c r="F197">
-        <v>54356000000</v>
+        <v>10475000000</v>
       </c>
       <c r="G197">
-        <v>3353000000</v>
+        <v>-712000000</v>
       </c>
       <c r="H197">
-        <v>271619000000</v>
+        <v>48028000000</v>
       </c>
       <c r="I197">
-        <v>330284000000</v>
+        <v>58029000000</v>
       </c>
       <c r="J197">
-        <v>17170000000</v>
+        <v>8188000000</v>
       </c>
       <c r="K197">
-        <v>704000000</v>
+        <v>262000000</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="B198">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C198" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D198">
-        <v>7442000000</v>
+        <v>8420000000</v>
       </c>
       <c r="E198">
-        <v>6785000000</v>
+        <v>7174000000</v>
       </c>
       <c r="F198">
-        <v>7051000000</v>
+        <v>8142000000</v>
       </c>
       <c r="G198">
-        <v>323000000</v>
+        <v>96000000</v>
       </c>
       <c r="H198">
-        <v>35567000000</v>
+        <v>47611000000</v>
       </c>
       <c r="I198">
-        <v>46052000000</v>
-      </c>
-      <c r="J198">
-        <v>4577000000</v>
+        <v>59808000000</v>
       </c>
       <c r="K198">
-        <v>71000000</v>
+        <v>28000000</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>2025</v>
-      </c>
-      <c r="B199" t="s">
-        <v>8</v>
+        <v>2017</v>
+      </c>
+      <c r="B199">
+        <v>2</v>
       </c>
       <c r="C199" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D199">
-        <v>28063000000</v>
+        <v>10000000000</v>
       </c>
       <c r="E199">
-        <v>25535000000</v>
+        <v>8622000000</v>
       </c>
       <c r="F199">
-        <v>27635000000</v>
+        <v>8601000000</v>
       </c>
       <c r="G199">
-        <v>441000000</v>
+        <v>818000000</v>
       </c>
       <c r="H199">
-        <v>139443000000</v>
+        <v>56356000000</v>
       </c>
       <c r="I199">
-        <v>180046000000</v>
-      </c>
-      <c r="J199">
-        <v>4577000000</v>
+        <v>67467000000</v>
       </c>
       <c r="K199">
-        <v>97000000</v>
+        <v>140000000</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="B200">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C200" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D200">
-        <v>13999000000</v>
+        <v>9878000000</v>
       </c>
       <c r="E200">
-        <v>12657000000</v>
+        <v>8528000000</v>
       </c>
       <c r="F200">
-        <v>13548000000</v>
+        <v>8786000000</v>
       </c>
       <c r="G200">
-        <v>99000000</v>
+        <v>637000000</v>
       </c>
       <c r="H200">
-        <v>61596000000</v>
+        <v>59145000000</v>
       </c>
       <c r="I200">
-        <v>74472000000</v>
-      </c>
-      <c r="J200">
-        <v>24639000000</v>
+        <v>70083000000</v>
       </c>
       <c r="K200">
-        <f>ROUND($K$201*(((D200-F200)/($D$201-$F$201))/(((D200-F200)/($D$201-$F$201))+((D188-F188)/($D$201-$F$201)))),0)</f>
-        <v>15639975</v>
+        <v>109000000</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>2025</v>
-      </c>
-      <c r="B201" t="s">
-        <v>8</v>
+        <v>2017</v>
+      </c>
+      <c r="B201">
+        <v>4</v>
       </c>
       <c r="C201" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D201">
-        <v>54633000000</v>
+        <v>9438000000</v>
       </c>
       <c r="E201">
-        <v>49643000000</v>
+        <v>8080000000</v>
       </c>
       <c r="F201">
-        <v>53166000000</v>
+        <v>8709000000</v>
       </c>
       <c r="G201">
-        <v>111000000</v>
+        <v>580000000</v>
       </c>
       <c r="H201">
-        <v>250294000000</v>
+        <v>53149000000</v>
       </c>
       <c r="I201">
-        <v>299411000000</v>
+        <v>65028000000</v>
       </c>
       <c r="J201">
-        <v>24639000000</v>
+        <v>11703000000</v>
       </c>
       <c r="K201">
-        <v>55000000</v>
+        <v>73000000</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>2026</v>
+        <v>2016</v>
       </c>
       <c r="B202">
         <v>1</v>
       </c>
       <c r="C202" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D202">
-        <v>15854000000</v>
+        <v>8195000000</v>
       </c>
       <c r="E202">
-        <v>12302000000</v>
+        <v>6990000000</v>
       </c>
       <c r="F202">
-        <v>15353000000</v>
+        <v>7546000000</v>
       </c>
       <c r="G202">
-        <v>-289000000</v>
+        <v>313000000</v>
       </c>
       <c r="H202">
-        <v>56470000000</v>
+        <v>46582000000</v>
       </c>
       <c r="I202">
-        <v>69163000000</v>
-      </c>
-      <c r="J202">
-        <v>10608000000</v>
+        <v>58273000000</v>
       </c>
       <c r="K202">
-        <v>165000000</v>
+        <v>94000000</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>2026</v>
+        <v>2016</v>
       </c>
       <c r="B203">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C203" t="s">
         <v>7</v>
       </c>
       <c r="D203">
-        <v>14608000000</v>
+        <v>9396000000</v>
       </c>
       <c r="E203">
-        <v>13166000000</v>
+        <v>8103000000</v>
       </c>
       <c r="F203">
-        <v>13611000000</v>
+        <v>8336000000</v>
       </c>
       <c r="G203">
-        <v>699000000</v>
+        <v>588000000</v>
       </c>
       <c r="H203">
-        <v>63385000000</v>
+        <v>54017000000</v>
       </c>
       <c r="I203">
-        <v>77698000000</v>
+        <v>64725000000</v>
       </c>
       <c r="K203">
-        <v>59000000</v>
+        <v>153000000</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>2026</v>
+        <v>2016</v>
       </c>
       <c r="B204">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C204" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D204">
-        <v>13912000000</v>
+        <v>9913000000</v>
       </c>
       <c r="E204">
-        <v>12495000000</v>
+        <v>8603000000</v>
       </c>
       <c r="F204">
-        <v>13953000000</v>
+        <v>8289000000</v>
       </c>
       <c r="G204">
-        <v>-382000000</v>
+        <v>965000000</v>
       </c>
       <c r="H204">
-        <v>58551000000</v>
+        <v>58172000000</v>
       </c>
       <c r="I204">
-        <v>72009000000</v>
-      </c>
-      <c r="J204">
-        <v>22934000000</v>
+        <v>68074000000</v>
       </c>
       <c r="K204">
-        <v>0</v>
+        <v>235000000</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>2026</v>
+        <v>2016</v>
       </c>
       <c r="B205">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C205" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D205">
-        <v>7249000000</v>
+        <v>9052000000</v>
       </c>
       <c r="E205">
-        <v>6591000000</v>
+        <v>7761000000</v>
       </c>
       <c r="F205">
-        <v>6919000000</v>
+        <v>8047000000</v>
       </c>
       <c r="G205">
-        <v>330000000</v>
+        <v>397000000</v>
       </c>
       <c r="H205">
-        <v>31151000000</v>
+        <v>51538000000</v>
       </c>
       <c r="I205">
-        <v>42049000000</v>
+        <v>62518000000</v>
       </c>
       <c r="J205">
-        <v>4536000000</v>
+        <v>9918000000</v>
       </c>
       <c r="K205">
-        <v>50000000</v>
+        <v>145000000</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>2026</v>
+        <v>2015</v>
       </c>
       <c r="B206">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C206" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D206">
-        <v>19757000000</v>
+        <v>8608000000</v>
       </c>
       <c r="E206">
-        <v>15607000000</v>
+        <v>7420000000</v>
       </c>
       <c r="F206">
-        <v>17893000000</v>
+        <v>7867000000</v>
       </c>
       <c r="G206">
-        <v>1604000000</v>
+        <v>508000000</v>
       </c>
       <c r="H206">
-        <v>66767000000</v>
+        <v>46444000000</v>
       </c>
       <c r="I206">
-        <v>78694000000</v>
-      </c>
-      <c r="J206">
-        <v>10101000000</v>
+        <v>57269000000</v>
       </c>
       <c r="K206">
-        <v>328000000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>2026</v>
+        <v>2015</v>
       </c>
       <c r="B207">
         <v>2</v>
@@ -8048,88 +7597,1463 @@
         <v>7</v>
       </c>
       <c r="D207">
-        <v>17672000000</v>
+        <v>9914000000</v>
       </c>
       <c r="E207">
-        <v>16100000000</v>
+        <v>8676000000</v>
       </c>
       <c r="F207">
-        <v>16576000000</v>
+        <v>8469000000</v>
       </c>
       <c r="G207">
-        <v>805000000</v>
+        <v>1193000000</v>
       </c>
       <c r="H207">
-        <v>72765000000</v>
+        <v>54289000000</v>
       </c>
       <c r="I207">
-        <v>87279000000</v>
+        <v>64685000000</v>
       </c>
       <c r="K207">
-        <v>90000000</v>
+        <v>195000000</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>2026</v>
+        <v>2015</v>
       </c>
       <c r="B208">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C208" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D208">
-        <v>16735000000</v>
+        <v>10306000000</v>
       </c>
       <c r="E208">
-        <v>15214000000</v>
+        <v>8960000000</v>
       </c>
       <c r="F208">
-        <v>16289000000</v>
+        <v>8407000000</v>
       </c>
       <c r="G208">
-        <v>71000000</v>
+        <v>4816000000</v>
       </c>
       <c r="H208">
-        <v>68118000000</v>
+        <v>57160000000</v>
       </c>
       <c r="I208">
-        <v>81843000000</v>
+        <v>66745000000</v>
       </c>
       <c r="K208">
-        <v>0</v>
+        <v>257000000</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209">
+        <v>2015</v>
+      </c>
+      <c r="B209">
+        <v>4</v>
+      </c>
+      <c r="C209" t="s">
+        <v>7</v>
+      </c>
+      <c r="D209">
+        <v>9036000000</v>
+      </c>
+      <c r="E209">
+        <v>7729000000</v>
+      </c>
+      <c r="F209">
+        <v>7955000000</v>
+      </c>
+      <c r="G209">
+        <v>823000000</v>
+      </c>
+      <c r="H209">
+        <v>50718000000</v>
+      </c>
+      <c r="I209">
+        <v>61304000000</v>
+      </c>
+      <c r="J209">
+        <v>9673000000</v>
+      </c>
+      <c r="K209">
+        <v>146000000</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>2014</v>
+      </c>
+      <c r="B210">
+        <v>1</v>
+      </c>
+      <c r="C210" t="s">
+        <v>7</v>
+      </c>
+      <c r="D210">
+        <v>8696000000</v>
+      </c>
+      <c r="E210">
+        <v>7384000000</v>
+      </c>
+      <c r="F210">
+        <v>9045000000</v>
+      </c>
+      <c r="G210">
+        <v>-609000000</v>
+      </c>
+      <c r="H210">
+        <v>46383000000</v>
+      </c>
+      <c r="I210">
+        <v>57216000000</v>
+      </c>
+      <c r="K210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>2014</v>
+      </c>
+      <c r="B211">
+        <v>2</v>
+      </c>
+      <c r="C211" t="s">
+        <v>7</v>
+      </c>
+      <c r="D211">
+        <v>10329000000</v>
+      </c>
+      <c r="E211">
+        <v>8981000000</v>
+      </c>
+      <c r="F211">
+        <v>9423000000</v>
+      </c>
+      <c r="G211">
+        <v>789000000</v>
+      </c>
+      <c r="H211">
+        <v>53900000000</v>
+      </c>
+      <c r="I211">
+        <v>63214000000</v>
+      </c>
+      <c r="K211">
+        <v>78000000</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>2014</v>
+      </c>
+      <c r="B212">
+        <v>3</v>
+      </c>
+      <c r="C212" t="s">
+        <v>7</v>
+      </c>
+      <c r="D212">
+        <v>10563000000</v>
+      </c>
+      <c r="E212">
+        <v>9314000000</v>
+      </c>
+      <c r="F212">
+        <v>9372000000</v>
+      </c>
+      <c r="G212">
+        <v>924000000</v>
+      </c>
+      <c r="H212">
+        <v>56065000000</v>
+      </c>
+      <c r="I212">
+        <v>65378000000</v>
+      </c>
+      <c r="K212">
+        <v>103000000</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>2014</v>
+      </c>
+      <c r="B213">
+        <v>4</v>
+      </c>
+      <c r="C213" t="s">
+        <v>7</v>
+      </c>
+      <c r="D213">
+        <v>9313000000</v>
+      </c>
+      <c r="E213">
+        <v>8083000000</v>
+      </c>
+      <c r="F213">
+        <v>8688000000</v>
+      </c>
+      <c r="G213">
+        <v>28000000</v>
+      </c>
+      <c r="H213">
+        <v>49211000000</v>
+      </c>
+      <c r="I213">
+        <v>60213000000</v>
+      </c>
+      <c r="J213">
+        <v>9953000000</v>
+      </c>
+      <c r="K213">
+        <v>54000000</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>2024</v>
+      </c>
+      <c r="B214">
+        <v>4</v>
+      </c>
+      <c r="C214" t="s">
+        <v>6</v>
+      </c>
+      <c r="D214">
+        <v>15559000000</v>
+      </c>
+      <c r="E214">
+        <v>12815000000</v>
+      </c>
+      <c r="F214">
+        <v>13842000000</v>
+      </c>
+      <c r="G214">
+        <v>843000000</v>
+      </c>
+      <c r="H214">
+        <v>60387000000</v>
+      </c>
+      <c r="I214">
+        <v>72035000000</v>
+      </c>
+      <c r="J214">
+        <v>13546000000</v>
+      </c>
+      <c r="K214">
+        <v>425000000</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>2024</v>
+      </c>
+      <c r="B215" t="s">
+        <v>8</v>
+      </c>
+      <c r="C215" t="s">
+        <v>6</v>
+      </c>
+      <c r="D215">
+        <v>61643000000</v>
+      </c>
+      <c r="E215">
+        <v>50894000000</v>
+      </c>
+      <c r="F215">
+        <v>55648000000</v>
+      </c>
+      <c r="G215">
+        <v>3457000000</v>
+      </c>
+      <c r="H215">
+        <v>246145000000</v>
+      </c>
+      <c r="I215">
+        <v>288394000000</v>
+      </c>
+      <c r="J215">
+        <v>13546000000</v>
+      </c>
+      <c r="K215">
+        <v>1389000000</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>2024</v>
+      </c>
+      <c r="B216">
+        <v>4</v>
+      </c>
+      <c r="C216" t="s">
+        <v>7</v>
+      </c>
+      <c r="D216">
+        <v>14695000000</v>
+      </c>
+      <c r="E216">
+        <v>13275000000</v>
+      </c>
+      <c r="F216">
+        <v>13192000000</v>
+      </c>
+      <c r="G216">
+        <v>985000000</v>
+      </c>
+      <c r="H216">
+        <v>64463000000</v>
+      </c>
+      <c r="I216">
+        <v>78298000000</v>
+      </c>
+      <c r="J216">
+        <v>21680000000</v>
+      </c>
+      <c r="K216">
+        <v>294000000</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>2024</v>
+      </c>
+      <c r="B217" t="s">
+        <v>8</v>
+      </c>
+      <c r="C217" t="s">
+        <v>7</v>
+      </c>
+      <c r="D217">
+        <v>57063000000</v>
+      </c>
+      <c r="E217">
+        <v>51829000000</v>
+      </c>
+      <c r="F217">
+        <v>51967000000</v>
+      </c>
+      <c r="G217">
+        <v>3149000000</v>
+      </c>
+      <c r="H217">
+        <v>258503000000</v>
+      </c>
+      <c r="I217">
+        <v>311185000000</v>
+      </c>
+      <c r="J217">
+        <v>21680000000</v>
+      </c>
+      <c r="K217">
+        <v>713000000</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>2024</v>
+      </c>
+      <c r="B218">
+        <v>4</v>
+      </c>
+      <c r="C218" t="s">
+        <v>5</v>
+      </c>
+      <c r="D218">
+        <v>13660000000</v>
+      </c>
+      <c r="E218">
+        <v>12402000000</v>
+      </c>
+      <c r="F218">
+        <v>12526000000</v>
+      </c>
+      <c r="G218">
+        <v>590000000</v>
+      </c>
+      <c r="H218">
+        <v>60676000000</v>
+      </c>
+      <c r="I218">
+        <v>71503000000</v>
+      </c>
+      <c r="J218">
+        <v>24617000000</v>
+      </c>
+      <c r="K218">
+        <f>ROUND($K$219*((D218-F218)/($D$219-$F$219)),0)</f>
+        <v>98910482</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>2024</v>
+      </c>
+      <c r="B219" t="s">
+        <v>8</v>
+      </c>
+      <c r="C219" t="s">
+        <v>5</v>
+      </c>
+      <c r="D219">
+        <v>54211000000</v>
+      </c>
+      <c r="E219">
+        <v>49586000000</v>
+      </c>
+      <c r="F219">
+        <v>51597000000</v>
+      </c>
+      <c r="G219">
+        <v>846000000</v>
+      </c>
+      <c r="H219">
+        <v>248795000000</v>
+      </c>
+      <c r="I219">
+        <v>292948000000</v>
+      </c>
+      <c r="J219">
+        <v>24617000000</v>
+      </c>
+      <c r="K219">
+        <v>228000000</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>2024</v>
+      </c>
+      <c r="B220">
+        <v>4</v>
+      </c>
+      <c r="C220" t="s">
+        <v>13</v>
+      </c>
+      <c r="D220">
+        <v>6931000000</v>
+      </c>
+      <c r="E220">
+        <v>6307000000</v>
+      </c>
+      <c r="F220">
+        <v>6653000000</v>
+      </c>
+      <c r="G220">
+        <v>261000000</v>
+      </c>
+      <c r="H220">
+        <v>34471000000</v>
+      </c>
+      <c r="I220">
+        <v>43533000000</v>
+      </c>
+      <c r="J220">
+        <v>5069000000</v>
+      </c>
+      <c r="K220">
+        <v>54000000</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>2024</v>
+      </c>
+      <c r="B221" t="s">
+        <v>8</v>
+      </c>
+      <c r="C221" t="s">
+        <v>13</v>
+      </c>
+      <c r="D221">
+        <v>27483000000</v>
+      </c>
+      <c r="E221">
+        <v>24980000000</v>
+      </c>
+      <c r="F221">
+        <v>27162000000</v>
+      </c>
+      <c r="G221">
+        <v>465000000</v>
+      </c>
+      <c r="H221">
+        <v>142515000000</v>
+      </c>
+      <c r="I221">
+        <v>177250000000</v>
+      </c>
+      <c r="J221">
+        <v>5069000000</v>
+      </c>
+      <c r="K221">
+        <v>103000000</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>2025</v>
+      </c>
+      <c r="B222">
+        <v>1</v>
+      </c>
+      <c r="C222" t="s">
+        <v>6</v>
+      </c>
+      <c r="D222">
+        <v>14040000000</v>
+      </c>
+      <c r="E222">
+        <v>11480000000</v>
+      </c>
+      <c r="F222">
+        <v>13471000000</v>
+      </c>
+      <c r="G222">
+        <v>240000000</v>
+      </c>
+      <c r="H222">
+        <v>55678000000</v>
+      </c>
+      <c r="I222">
+        <v>68401000000</v>
+      </c>
+      <c r="J222">
+        <v>12432000000</v>
+      </c>
+      <c r="K222">
+        <v>124000000</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>2025</v>
+      </c>
+      <c r="B223">
+        <v>1</v>
+      </c>
+      <c r="C223" t="s">
+        <v>7</v>
+      </c>
+      <c r="D223">
+        <v>13213000000</v>
+      </c>
+      <c r="E223">
+        <v>11860000000</v>
+      </c>
+      <c r="F223">
+        <v>12605000000</v>
+      </c>
+      <c r="G223">
+        <v>387000000</v>
+      </c>
+      <c r="H223">
+        <v>59517000000</v>
+      </c>
+      <c r="I223">
+        <v>75155000000</v>
+      </c>
+      <c r="K223">
+        <v>43000000</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>2025</v>
+      </c>
+      <c r="B224">
+        <v>1</v>
+      </c>
+      <c r="C224" t="s">
+        <v>5</v>
+      </c>
+      <c r="D224">
+        <v>12551000000</v>
+      </c>
+      <c r="E224">
+        <v>11391000000</v>
+      </c>
+      <c r="F224">
+        <v>12821000000</v>
+      </c>
+      <c r="G224">
+        <v>-473000000</v>
+      </c>
+      <c r="H224">
+        <v>56356000000</v>
+      </c>
+      <c r="I224">
+        <v>69904000000</v>
+      </c>
+      <c r="J224">
+        <v>24705000000</v>
+      </c>
+      <c r="K224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>2025</v>
+      </c>
+      <c r="B225">
+        <v>1</v>
+      </c>
+      <c r="C225" t="s">
+        <v>13</v>
+      </c>
+      <c r="D225">
+        <v>6428000000</v>
+      </c>
+      <c r="E225">
+        <v>5811000000</v>
+      </c>
+      <c r="F225">
+        <v>6651000000</v>
+      </c>
+      <c r="G225">
+        <v>-149000000</v>
+      </c>
+      <c r="H225">
+        <v>30629000000</v>
+      </c>
+      <c r="I225">
+        <v>41432000000</v>
+      </c>
+      <c r="J225">
+        <v>4086000000</v>
+      </c>
+      <c r="K225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>2025</v>
+      </c>
+      <c r="B226">
+        <v>2</v>
+      </c>
+      <c r="C226" t="s">
+        <v>6</v>
+      </c>
+      <c r="D226">
+        <v>16648000000</v>
+      </c>
+      <c r="E226">
+        <v>13867000000</v>
+      </c>
+      <c r="F226">
+        <v>14546000000</v>
+      </c>
+      <c r="G226">
+        <v>2130000000</v>
+      </c>
+      <c r="H226">
+        <v>66417000000</v>
+      </c>
+      <c r="I226">
+        <v>77645000000</v>
+      </c>
+      <c r="J226">
+        <v>12400000000</v>
+      </c>
+      <c r="K226">
+        <v>470000000</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>2025</v>
+      </c>
+      <c r="B227">
+        <v>2</v>
+      </c>
+      <c r="C227" t="s">
+        <v>7</v>
+      </c>
+      <c r="D227">
+        <v>15236000000</v>
+      </c>
+      <c r="E227">
+        <v>13836000000</v>
+      </c>
+      <c r="F227">
+        <v>13911000000</v>
+      </c>
+      <c r="G227">
+        <v>973000000</v>
+      </c>
+      <c r="H227">
+        <v>70088000000</v>
+      </c>
+      <c r="I227">
+        <v>84347000000</v>
+      </c>
+      <c r="K227">
+        <v>188000000</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>2025</v>
+      </c>
+      <c r="B228">
+        <v>2</v>
+      </c>
+      <c r="C228" t="s">
+        <v>5</v>
+      </c>
+      <c r="D228">
+        <v>14392000000</v>
+      </c>
+      <c r="E228">
+        <v>13123000000</v>
+      </c>
+      <c r="F228">
+        <v>13257000000</v>
+      </c>
+      <c r="G228">
+        <v>599000000</v>
+      </c>
+      <c r="H228">
+        <v>65762000000</v>
+      </c>
+      <c r="I228">
+        <v>77636000000</v>
+      </c>
+      <c r="J228">
+        <v>24217000000</v>
+      </c>
+      <c r="K228">
+        <v>41000000</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>2025</v>
+      </c>
+      <c r="B229">
+        <v>2</v>
+      </c>
+      <c r="C229" t="s">
+        <v>13</v>
+      </c>
+      <c r="D229">
+        <v>7244000000</v>
+      </c>
+      <c r="E229">
+        <v>6627000000</v>
+      </c>
+      <c r="F229">
+        <v>7019000000</v>
+      </c>
+      <c r="G229">
+        <v>213000000</v>
+      </c>
+      <c r="H229">
+        <v>36885000000</v>
+      </c>
+      <c r="I229">
+        <v>46996000000</v>
+      </c>
+      <c r="J229">
+        <v>4081000000</v>
+      </c>
+      <c r="K229">
+        <v>14000000</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>2025</v>
+      </c>
+      <c r="B230">
+        <v>3</v>
+      </c>
+      <c r="C230" t="s">
+        <v>6</v>
+      </c>
+      <c r="D230">
+        <v>16673000000</v>
+      </c>
+      <c r="E230">
+        <v>13506000000</v>
+      </c>
+      <c r="F230">
+        <v>14989000000</v>
+      </c>
+      <c r="G230">
+        <v>1417000000</v>
+      </c>
+      <c r="H230">
+        <v>67621000000</v>
+      </c>
+      <c r="I230">
+        <v>79054000000</v>
+      </c>
+      <c r="J230">
+        <v>12299000000</v>
+      </c>
+      <c r="K230">
+        <v>392000000</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>2025</v>
+      </c>
+      <c r="B231">
+        <v>3</v>
+      </c>
+      <c r="C231" t="s">
+        <v>7</v>
+      </c>
+      <c r="D231">
+        <v>15225000000</v>
+      </c>
+      <c r="E231">
+        <v>13815000000</v>
+      </c>
+      <c r="F231">
+        <v>13830000000</v>
+      </c>
+      <c r="G231">
+        <v>949000000</v>
+      </c>
+      <c r="H231">
+        <v>73769000000</v>
+      </c>
+      <c r="I231">
+        <v>87417000000</v>
+      </c>
+      <c r="K231">
+        <v>228000000</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>2025</v>
+      </c>
+      <c r="B232">
+        <v>3</v>
+      </c>
+      <c r="C232" t="s">
+        <v>5</v>
+      </c>
+      <c r="D232">
+        <v>13691000000</v>
+      </c>
+      <c r="E232">
+        <v>12471000000</v>
+      </c>
+      <c r="F232">
+        <v>13540000000</v>
+      </c>
+      <c r="G232">
+        <v>-114000000</v>
+      </c>
+      <c r="H232">
+        <v>66580000000</v>
+      </c>
+      <c r="I232">
+        <v>77400000000</v>
+      </c>
+      <c r="J232">
+        <v>24538000000</v>
+      </c>
+      <c r="K232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>2025</v>
+      </c>
+      <c r="B233">
+        <v>3</v>
+      </c>
+      <c r="C233" t="s">
+        <v>13</v>
+      </c>
+      <c r="D233">
+        <v>6949000000</v>
+      </c>
+      <c r="E233">
+        <v>6313000000</v>
+      </c>
+      <c r="F233">
+        <v>6914000000</v>
+      </c>
+      <c r="G233">
+        <v>54000000</v>
+      </c>
+      <c r="H233">
+        <v>36362000000</v>
+      </c>
+      <c r="I233">
+        <v>45567000000</v>
+      </c>
+      <c r="J233">
+        <v>4079000000</v>
+      </c>
+      <c r="K233">
+        <v>11000000</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>2025</v>
+      </c>
+      <c r="B234">
+        <v>4</v>
+      </c>
+      <c r="C234" t="s">
+        <v>6</v>
+      </c>
+      <c r="D234">
+        <v>16003000000</v>
+      </c>
+      <c r="E234">
+        <v>12916000000</v>
+      </c>
+      <c r="F234">
+        <v>14536000000</v>
+      </c>
+      <c r="G234">
+        <v>1219000000</v>
+      </c>
+      <c r="H234">
+        <v>59861000000</v>
+      </c>
+      <c r="I234">
+        <v>72946000000</v>
+      </c>
+      <c r="J234">
+        <v>11936000000</v>
+      </c>
+      <c r="K234">
+        <v>351000000</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>2025</v>
+      </c>
+      <c r="B235" t="s">
+        <v>8</v>
+      </c>
+      <c r="C235" t="s">
+        <v>6</v>
+      </c>
+      <c r="D235">
+        <v>63364000000</v>
+      </c>
+      <c r="E235">
+        <v>51768000000</v>
+      </c>
+      <c r="F235">
+        <v>57542000000</v>
+      </c>
+      <c r="G235">
+        <v>5005000000</v>
+      </c>
+      <c r="H235">
+        <v>249578000000</v>
+      </c>
+      <c r="I235">
+        <v>298045000000</v>
+      </c>
+      <c r="J235">
+        <v>11936000000</v>
+      </c>
+      <c r="K235">
+        <v>1337000000</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>2025</v>
+      </c>
+      <c r="B236">
+        <v>4</v>
+      </c>
+      <c r="C236" t="s">
+        <v>7</v>
+      </c>
+      <c r="D236">
+        <v>15397000000</v>
+      </c>
+      <c r="E236">
+        <v>13926000000</v>
+      </c>
+      <c r="F236">
+        <v>14011000000</v>
+      </c>
+      <c r="G236">
+        <v>1044000000</v>
+      </c>
+      <c r="H236">
+        <v>68246000000</v>
+      </c>
+      <c r="I236">
+        <v>83365000000</v>
+      </c>
+      <c r="J236">
+        <v>17170000000</v>
+      </c>
+      <c r="K236">
+        <v>244000000</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>2025</v>
+      </c>
+      <c r="B237" t="s">
+        <v>8</v>
+      </c>
+      <c r="C237" t="s">
+        <v>7</v>
+      </c>
+      <c r="D237">
+        <v>59070000000</v>
+      </c>
+      <c r="E237">
+        <v>53438000000</v>
+      </c>
+      <c r="F237">
+        <v>54356000000</v>
+      </c>
+      <c r="G237">
+        <v>3353000000</v>
+      </c>
+      <c r="H237">
+        <v>271619000000</v>
+      </c>
+      <c r="I237">
+        <v>330284000000</v>
+      </c>
+      <c r="J237">
+        <v>17170000000</v>
+      </c>
+      <c r="K237">
+        <v>704000000</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>2025</v>
+      </c>
+      <c r="B238">
+        <v>4</v>
+      </c>
+      <c r="C238" t="s">
+        <v>13</v>
+      </c>
+      <c r="D238">
+        <v>7442000000</v>
+      </c>
+      <c r="E238">
+        <v>6785000000</v>
+      </c>
+      <c r="F238">
+        <v>7051000000</v>
+      </c>
+      <c r="G238">
+        <v>323000000</v>
+      </c>
+      <c r="H238">
+        <v>35567000000</v>
+      </c>
+      <c r="I238">
+        <v>46052000000</v>
+      </c>
+      <c r="J238">
+        <v>4577000000</v>
+      </c>
+      <c r="K238">
+        <v>71000000</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>2025</v>
+      </c>
+      <c r="B239" t="s">
+        <v>8</v>
+      </c>
+      <c r="C239" t="s">
+        <v>13</v>
+      </c>
+      <c r="D239">
+        <v>28063000000</v>
+      </c>
+      <c r="E239">
+        <v>25535000000</v>
+      </c>
+      <c r="F239">
+        <v>27635000000</v>
+      </c>
+      <c r="G239">
+        <v>441000000</v>
+      </c>
+      <c r="H239">
+        <v>139443000000</v>
+      </c>
+      <c r="I239">
+        <v>180046000000</v>
+      </c>
+      <c r="J239">
+        <v>4577000000</v>
+      </c>
+      <c r="K239">
+        <v>97000000</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>2025</v>
+      </c>
+      <c r="B240">
+        <v>4</v>
+      </c>
+      <c r="C240" t="s">
+        <v>5</v>
+      </c>
+      <c r="D240">
+        <v>13999000000</v>
+      </c>
+      <c r="E240">
+        <v>12657000000</v>
+      </c>
+      <c r="F240">
+        <v>13548000000</v>
+      </c>
+      <c r="G240">
+        <v>99000000</v>
+      </c>
+      <c r="H240">
+        <v>61596000000</v>
+      </c>
+      <c r="I240">
+        <v>74472000000</v>
+      </c>
+      <c r="J240">
+        <v>24639000000</v>
+      </c>
+      <c r="K240">
+        <f>ROUND($K$241*(((D240-F240)/($D$241-$F$241))/(((D240-F240)/($D$241-$F$241))+((D228-F228)/($D$241-$F$241)))),0)</f>
+        <v>15639975</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>2025</v>
+      </c>
+      <c r="B241" t="s">
+        <v>8</v>
+      </c>
+      <c r="C241" t="s">
+        <v>5</v>
+      </c>
+      <c r="D241">
+        <v>54633000000</v>
+      </c>
+      <c r="E241">
+        <v>49643000000</v>
+      </c>
+      <c r="F241">
+        <v>53166000000</v>
+      </c>
+      <c r="G241">
+        <v>111000000</v>
+      </c>
+      <c r="H241">
+        <v>250294000000</v>
+      </c>
+      <c r="I241">
+        <v>299411000000</v>
+      </c>
+      <c r="J241">
+        <v>24639000000</v>
+      </c>
+      <c r="K241">
+        <v>55000000</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A242">
         <v>2026</v>
       </c>
-      <c r="B209">
+      <c r="B242">
+        <v>1</v>
+      </c>
+      <c r="C242" t="s">
+        <v>6</v>
+      </c>
+      <c r="D242">
+        <v>15854000000</v>
+      </c>
+      <c r="E242">
+        <v>12302000000</v>
+      </c>
+      <c r="F242">
+        <v>15353000000</v>
+      </c>
+      <c r="G242">
+        <v>-289000000</v>
+      </c>
+      <c r="H242">
+        <v>56470000000</v>
+      </c>
+      <c r="I242">
+        <v>69163000000</v>
+      </c>
+      <c r="J242">
+        <v>10608000000</v>
+      </c>
+      <c r="K242">
+        <v>165000000</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>2026</v>
+      </c>
+      <c r="B243">
+        <v>1</v>
+      </c>
+      <c r="C243" t="s">
+        <v>7</v>
+      </c>
+      <c r="D243">
+        <v>14608000000</v>
+      </c>
+      <c r="E243">
+        <v>13166000000</v>
+      </c>
+      <c r="F243">
+        <v>13611000000</v>
+      </c>
+      <c r="G243">
+        <v>699000000</v>
+      </c>
+      <c r="H243">
+        <v>63385000000</v>
+      </c>
+      <c r="I243">
+        <v>77698000000</v>
+      </c>
+      <c r="K243">
+        <v>59000000</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>2026</v>
+      </c>
+      <c r="B244">
+        <v>1</v>
+      </c>
+      <c r="C244" t="s">
+        <v>5</v>
+      </c>
+      <c r="D244">
+        <v>13912000000</v>
+      </c>
+      <c r="E244">
+        <v>12495000000</v>
+      </c>
+      <c r="F244">
+        <v>13953000000</v>
+      </c>
+      <c r="G244">
+        <v>-382000000</v>
+      </c>
+      <c r="H244">
+        <v>58551000000</v>
+      </c>
+      <c r="I244">
+        <v>72009000000</v>
+      </c>
+      <c r="J244">
+        <v>22934000000</v>
+      </c>
+      <c r="K244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>2026</v>
+      </c>
+      <c r="B245">
+        <v>1</v>
+      </c>
+      <c r="C245" t="s">
+        <v>13</v>
+      </c>
+      <c r="D245">
+        <v>7249000000</v>
+      </c>
+      <c r="E245">
+        <v>6591000000</v>
+      </c>
+      <c r="F245">
+        <v>6919000000</v>
+      </c>
+      <c r="G245">
+        <v>330000000</v>
+      </c>
+      <c r="H245">
+        <v>31151000000</v>
+      </c>
+      <c r="I245">
+        <v>42049000000</v>
+      </c>
+      <c r="J245">
+        <v>4536000000</v>
+      </c>
+      <c r="K245">
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>2026</v>
+      </c>
+      <c r="B246">
         <v>2</v>
       </c>
-      <c r="C209" t="s">
+      <c r="C246" t="s">
+        <v>6</v>
+      </c>
+      <c r="D246">
+        <v>19757000000</v>
+      </c>
+      <c r="E246">
+        <v>15607000000</v>
+      </c>
+      <c r="F246">
+        <v>17893000000</v>
+      </c>
+      <c r="G246">
+        <v>1604000000</v>
+      </c>
+      <c r="H246">
+        <v>66767000000</v>
+      </c>
+      <c r="I246">
+        <v>78694000000</v>
+      </c>
+      <c r="J246">
+        <v>10101000000</v>
+      </c>
+      <c r="K246">
+        <v>328000000</v>
+      </c>
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>2026</v>
+      </c>
+      <c r="B247">
+        <v>2</v>
+      </c>
+      <c r="C247" t="s">
+        <v>7</v>
+      </c>
+      <c r="D247">
+        <v>17672000000</v>
+      </c>
+      <c r="E247">
+        <v>16100000000</v>
+      </c>
+      <c r="F247">
+        <v>16576000000</v>
+      </c>
+      <c r="G247">
+        <v>805000000</v>
+      </c>
+      <c r="H247">
+        <v>72765000000</v>
+      </c>
+      <c r="I247">
+        <v>87279000000</v>
+      </c>
+      <c r="K247">
+        <v>90000000</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>2026</v>
+      </c>
+      <c r="B248">
+        <v>2</v>
+      </c>
+      <c r="C248" t="s">
+        <v>5</v>
+      </c>
+      <c r="D248">
+        <v>16735000000</v>
+      </c>
+      <c r="E248">
+        <v>15214000000</v>
+      </c>
+      <c r="F248">
+        <v>16289000000</v>
+      </c>
+      <c r="G248">
+        <v>71000000</v>
+      </c>
+      <c r="H248">
+        <v>68118000000</v>
+      </c>
+      <c r="I248">
+        <v>81843000000</v>
+      </c>
+      <c r="K248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>2026</v>
+      </c>
+      <c r="B249">
+        <v>2</v>
+      </c>
+      <c r="C249" t="s">
         <v>13</v>
       </c>
-      <c r="D209">
+      <c r="D249">
         <v>8432000000</v>
       </c>
-      <c r="E209">
+      <c r="E249">
         <v>7745000000</v>
       </c>
-      <c r="F209">
+      <c r="F249">
         <v>8147000000</v>
       </c>
-      <c r="G209">
-        <v>285000000</v>
-      </c>
-      <c r="H209">
+      <c r="G249">
+        <v>233000000</v>
+      </c>
+      <c r="H249">
         <v>37346000000</v>
       </c>
-      <c r="I209">
+      <c r="I249">
         <v>47093000000</v>
       </c>
-      <c r="K209">
+      <c r="K249">
         <v>53000000</v>
       </c>
     </row>

--- a/airline-dashboard/data/manual/airline_financial_data.xlsx
+++ b/airline-dashboard/data/manual/airline_financial_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0f26b992e1a44723/Documents/GitHub Repos/airline_financials/airline-dashboard/data/manual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{826EDDCB-8DC5-48D4-92ED-2287CEBE3206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{623539DB-94CE-4819-82FE-06D2F853BFFB}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{826EDDCB-8DC5-48D4-92ED-2287CEBE3206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{129EAC36-BC35-44AC-9E23-3A745FA3494D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CC2E0DD-0C2A-471D-BE08-E27D8B31800B}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="23">
   <si>
     <t>Year</t>
   </si>
@@ -95,6 +95,15 @@
   </si>
   <si>
     <t>Operating Expenses</t>
+  </si>
+  <si>
+    <t>ALK</t>
+  </si>
+  <si>
+    <t>JBLU</t>
+  </si>
+  <si>
+    <t>HA</t>
   </si>
 </sst>
 </file>
@@ -639,10 +648,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -960,7 +965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95BF35CD-6CF2-4D2E-9294-3A1A732D8FBE}">
-  <dimension ref="A1:K249"/>
+  <dimension ref="A1:K264"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
@@ -9055,6 +9060,216 @@
       </c>
       <c r="K249">
         <v>53000000</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>2018</v>
+      </c>
+      <c r="B250">
+        <v>1</v>
+      </c>
+      <c r="C250" t="s">
+        <v>20</v>
+      </c>
+      <c r="E250">
+        <v>1684000000</v>
+      </c>
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>2018</v>
+      </c>
+      <c r="B251">
+        <v>2</v>
+      </c>
+      <c r="C251" t="s">
+        <v>20</v>
+      </c>
+      <c r="E251">
+        <v>1997000000</v>
+      </c>
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>2018</v>
+      </c>
+      <c r="B252">
+        <v>3</v>
+      </c>
+      <c r="C252" t="s">
+        <v>20</v>
+      </c>
+      <c r="E252">
+        <v>2043000000</v>
+      </c>
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>2018</v>
+      </c>
+      <c r="B253">
+        <v>4</v>
+      </c>
+      <c r="C253" t="s">
+        <v>20</v>
+      </c>
+      <c r="E253">
+        <v>1907000000</v>
+      </c>
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>2018</v>
+      </c>
+      <c r="B254" t="s">
+        <v>8</v>
+      </c>
+      <c r="C254" t="s">
+        <v>20</v>
+      </c>
+      <c r="E254">
+        <v>7631000000</v>
+      </c>
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>2018</v>
+      </c>
+      <c r="B255">
+        <v>1</v>
+      </c>
+      <c r="C255" t="s">
+        <v>21</v>
+      </c>
+      <c r="E255">
+        <v>1692000000</v>
+      </c>
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>2018</v>
+      </c>
+      <c r="B256">
+        <v>2</v>
+      </c>
+      <c r="C256" t="s">
+        <v>21</v>
+      </c>
+      <c r="E256">
+        <v>1858000000</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>2018</v>
+      </c>
+      <c r="B257">
+        <v>3</v>
+      </c>
+      <c r="C257" t="s">
+        <v>21</v>
+      </c>
+      <c r="E257">
+        <v>1941000000</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>2018</v>
+      </c>
+      <c r="B258">
+        <v>4</v>
+      </c>
+      <c r="C258" t="s">
+        <v>21</v>
+      </c>
+      <c r="E258">
+        <v>1891000000</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>2018</v>
+      </c>
+      <c r="B259" t="s">
+        <v>8</v>
+      </c>
+      <c r="C259" t="s">
+        <v>21</v>
+      </c>
+      <c r="E259">
+        <v>7381000000</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>2018</v>
+      </c>
+      <c r="B260">
+        <v>1</v>
+      </c>
+      <c r="C260" t="s">
+        <v>22</v>
+      </c>
+      <c r="E260">
+        <v>611600000</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>2018</v>
+      </c>
+      <c r="B261">
+        <v>2</v>
+      </c>
+      <c r="C261" t="s">
+        <v>22</v>
+      </c>
+      <c r="E261">
+        <v>655162000</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>2018</v>
+      </c>
+      <c r="B262">
+        <v>3</v>
+      </c>
+      <c r="C262" t="s">
+        <v>22</v>
+      </c>
+      <c r="E262">
+        <v>697232000</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>2018</v>
+      </c>
+      <c r="B263">
+        <v>4</v>
+      </c>
+      <c r="C263" t="s">
+        <v>22</v>
+      </c>
+      <c r="E263">
+        <v>638799000</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>2018</v>
+      </c>
+      <c r="B264" t="s">
+        <v>8</v>
+      </c>
+      <c r="C264" t="s">
+        <v>22</v>
+      </c>
+      <c r="E264">
+        <v>2602793000</v>
       </c>
     </row>
   </sheetData>
